--- a/24-spacex-ipo-quality-model/spacex_ipo_quality_model.xlsx
+++ b/24-spacex-ipo-quality-model/spacex_ipo_quality_model.xlsx
@@ -11,19 +11,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="offering_math" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shareholder_ratios" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lockup_calendar" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quality_scores" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="comp_universe" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="comp_ipo_performance" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ipo_chase_base_rate" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ipo_chase_sector_base_rate" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="combined_ipo_decision_bridge" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="underwriter_quality" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="segment_quality" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="valuation_sensitivity" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="excluded_comps" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="index_inclusion_rules" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="index_inclusion_timeline" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lockup_supply_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lockup_first_6m_scenarios" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quality_scores" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="comp_universe" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="comp_ipo_performance" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ipo_chase_base_rate" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ipo_chase_sector_base_rate" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="combined_ipo_decision_bridge" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="underwriter_quality" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="segment_quality" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="valuation_sensitivity" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="excluded_comps" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="index_inclusion_rules" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="index_inclusion_timeline" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -967,141 +969,160 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>layer</t>
+          <t>horizon_days</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>positive_pct</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>median_abs_return_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>mean_abs_return_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>median_excess_vs_spy_pct</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>beat_spy_pct</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>source</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>finding</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>key_number</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>spacex_decision_rule</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Broad IPO prior</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Study 15</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Day-1-close IPO chasing is a negative base-rate trade.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>365d median excess vs SPY -28.4%; only 19% beat SPY.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Start from skepticism; do not buy SpaceX just because the IPO is famous.</t>
+      <c r="A2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B2" t="n">
+        <v>760</v>
+      </c>
+      <c r="C2" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>YehCapital study 15; day-1-close entries for 760 US IPOs since 2022-10</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Quality filter</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Study 24</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Small/noisy IPOs are removed; only institutional-scale comps remain.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Filtered 6m comp median from first close -14.7%.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Quality filter reduces junk risk but still leaves post-IPO fade risk.</t>
+      <c r="A3" t="n">
+        <v>90</v>
+      </c>
+      <c r="B3" t="n">
+        <v>731</v>
+      </c>
+      <c r="C3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>29</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>YehCapital study 15; day-1-close entries for 760 US IPOs since 2022-10</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Scarcity and index flow</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Study 24</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SpaceX has unusually tight immediate tradable supply plus a Nasdaq-100 fast-entry path.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Immediate float 4.25%; Nasdaq low-float modified market cap about $225B.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Treat early upside as flow/scarcity, not proof of long-term entry quality.</t>
+      <c r="A4" t="n">
+        <v>180</v>
+      </c>
+      <c r="B4" t="n">
+        <v>641</v>
+      </c>
+      <c r="C4" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-11.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>YehCapital study 15; day-1-close entries for 760 US IPOs since 2022-10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Unlock and governance penalty</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Study 24</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>First-six-month releases, Musk control and registration-rights overhang cap public-entry quality.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Q2/Q3 earnings unlocks plus 70/90/105/120/135/180-day releases are multiples of IPO float.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Wait for unlock absorption before underwriting a larger long-term position.</t>
+      <c r="A5" t="n">
+        <v>365</v>
+      </c>
+      <c r="B5" t="n">
+        <v>474</v>
+      </c>
+      <c r="C5" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-28.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>19</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>YehCapital study 15; day-1-close entries for 760 US IPOs since 2022-10</t>
         </is>
       </c>
     </row>
@@ -1116,448 +1137,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>underwriter</t>
+          <t>sector</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>n</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>quality_score</t>
+          <t>positive_90d_pct</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>median_90d_return_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>median_365d_return_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>spacex_model_read</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Joint bookrunner / lead-left group</t>
-        </is>
+          <t>Software / IT</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Top-tier mega-cap IPO franchise and stabilization credibility.</t>
+        <v>65.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Survivor bucket in study 15; closest public-market analogue to profitable infrastructure/software quality.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>YehCapital study 15 sector table</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Joint bookrunner / lead-left group</t>
-        </is>
+          <t>Real Estate / REIT</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>192</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Top-tier technology IPO franchise; stabilization agent per S-1/A.</t>
+        <v>79.8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Survivor bucket but not comparable to SpaceX business quality or capital cycle.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>YehCapital study 15 sector table</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BofA Securities</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Joint bookrunner</t>
-        </is>
+          <t>Biotech / Pharma</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>53</v>
       </c>
       <c r="C4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Top global distribution and lending relationship.</t>
+        <v>32.1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-13</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Explicitly excluded from the SpaceX comp set.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>YehCapital study 15 sector table</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Citigroup</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Joint bookrunner</t>
-        </is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Top global distribution; strong cross-border reach.</t>
+        <v>47.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-63.4</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Too small/noisy as a broad bucket; not a mega-cap aerospace/space comp.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>YehCapital study 15 sector table</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J.P. Morgan</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Joint bookrunner</t>
-        </is>
+          <t>Micro-cap / unclassified</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>324</v>
       </c>
       <c r="C6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Top global equity capital markets franchise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Barclays</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Joint bookrunner</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Strong global technology/industrial ECM distribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Deutsche Bank Securities</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Joint bookrunner</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Global bank; useful international distribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Wells Fargo Securities</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Large U.S. distribution and lending relationship.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Allen &amp; Company</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Elite tech/media relationship bank; narrower distribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Cantor</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Distribution support; not lead franchise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Needham</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Growth/technology distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Raymond James</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Retail and middle-market distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Societe Generale</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>European distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Stifel</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Retail and growth distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>William Blair</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Growth-company distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>BTG Pactual</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Latin America distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ING</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>European distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Macquarie Capital</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Asia-Pacific/infrastructure distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Mirae Asset Securities</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Asia distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Mizuho</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Japan/global distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>European/Latin America distribution support.</t>
+        <v>43.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-63.7</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Explicitly excluded from the SpaceX comp set.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>YehCapital study 15 sector table</t>
         </is>
       </c>
     </row>
@@ -1572,209 +1333,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>segment</t>
+          <t>layer</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>revenue_2025_usd_b</t>
+          <t>source</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>operating_income_2025_usd_b</t>
+          <t>finding</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>adjusted_ebitda_2025_usd_b</t>
+          <t>key_number</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>capex_2025_usd_b</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>revenue_q1_2026_usd_b</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>operating_income_q1_2026_usd_b</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>adjusted_ebitda_q1_2026_usd_b</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>capex_q1_2026_usd_b</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>business_quality_score</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>operating_margin_2025_pct</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>capex_to_revenue_2025_pct</t>
+          <t>spacex_decision_rule</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Space</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>4.086</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.657</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.653</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3.832</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-0.662</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-0.351</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.052</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Launch cadence and vertical integration are elite; still loss-making in Q1 and Starship execution is key.</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>-16.07929515418502</v>
-      </c>
-      <c r="M2" t="n">
-        <v>93.78365149290261</v>
+          <t>Broad IPO prior</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Study 15</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Day-1-close IPO chasing is a negative base-rate trade.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>365d median excess vs SPY -28.4%; only 19% beat SPY.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Start from skepticism; do not buy SpaceX just because the IPO is famous.</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Connectivity</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>11.387</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4.423</v>
-      </c>
-      <c r="D3" t="n">
-        <v>7.168</v>
-      </c>
-      <c r="E3" t="n">
-        <v>4.178</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3.257</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.188</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.087</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.332</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Best current business: 2025 operating margin 38.8%, subscribers 8.9M at year-end and 10.3M Q1 2026; ARPU declining from $99 in 2023 to $66 Q1 2026.</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>38.84253973829806</v>
-      </c>
-      <c r="M3" t="n">
-        <v>36.69096337929217</v>
+          <t>Quality filter</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Study 24</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Small/noisy IPOs are removed; only institutional-scale comps remain.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Filtered 6m comp median from first close -14.7%.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Quality filter reduces junk risk but still leaves post-IPO fade risk.</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI/xAI/X</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.201</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-6.355</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-1.237</v>
-      </c>
-      <c r="E4" t="n">
-        <v>12.727</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.8179999999999999</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-2.469</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-0.609</v>
-      </c>
-      <c r="I4" t="n">
-        <v>7.723</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Biggest upside and biggest quality penalty: $12.7B 2025 capex, large operating losses, related-party and regulatory complexity; Anthropic/Google contracts improve revenue visibility but are terminable.</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>-198.5317088409872</v>
-      </c>
-      <c r="M4" t="n">
-        <v>397.5945017182131</v>
+          <t>Scarcity and index flow</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Study 24</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SpaceX has unusually tight immediate tradable supply plus a Nasdaq-100 fast-entry path.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Immediate float 4.25%; Nasdaq low-float modified market cap about $225B.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Treat early upside as flow/scarcity, not proof of long-term entry quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Unlock and governance penalty</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Study 24</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>First-six-month releases, Musk control and registration-rights overhang cap public-entry quality.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Q2/Q3 earnings unlocks plus 70/90/105/120/135/180-day releases are multiples of IPO float.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Wait for unlock absorption before underwriting a larger long-term position.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1788,31 +1482,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>case</t>
+          <t>underwriter</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>revenue_usd_b</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>implied_market_cap_usd_b</t>
+          <t>quality_score</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>price_to_sales_x</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1821,84 +1510,420 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025 reported revenue</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>18.674</v>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Joint bookrunner / lead-left group</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>1765.241798625</v>
-      </c>
-      <c r="D2" t="n">
-        <v>94.52938838090392</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Contract run-rate cases are not risk-adjusted; Anthropic/Google contracts are terminable and delivery-dependent.</t>
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Top-tier mega-cap IPO franchise and stabilization credibility.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Q1 2026 annualized</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>18.776</v>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Joint bookrunner / lead-left group</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>1765.241798625</v>
-      </c>
-      <c r="D3" t="n">
-        <v>94.01586059996804</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Contract run-rate cases are not risk-adjusted; Anthropic/Google contracts are terminable and delivery-dependent.</t>
+        <v>5</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Top-tier technology IPO franchise; stabilization agent per S-1/A.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025 revenue + Anthropic annualized run-rate</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>33.674</v>
+          <t>BofA Securities</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Joint bookrunner</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>1765.241798625</v>
-      </c>
-      <c r="D4" t="n">
-        <v>52.42150616573617</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Contract run-rate cases are not risk-adjusted; Anthropic/Google contracts are terminable and delivery-dependent.</t>
+        <v>4.5</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Top global distribution and lending relationship.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025 revenue + Anthropic + Google annualized run-rate</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>44.714</v>
+          <t>Citigroup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Joint bookrunner</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>1765.241798625</v>
-      </c>
-      <c r="D5" t="n">
-        <v>39.47850334626738</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Contract run-rate cases are not risk-adjusted; Anthropic/Google contracts are terminable and delivery-dependent.</t>
+        <v>4.5</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Top global distribution; strong cross-border reach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>J.P. Morgan</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Joint bookrunner</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Top global equity capital markets franchise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Barclays</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Joint bookrunner</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Strong global technology/industrial ECM distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Securities</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Joint bookrunner</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Global bank; useful international distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Wells Fargo Securities</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Large U.S. distribution and lending relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Allen &amp; Company</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Elite tech/media relationship bank; narrower distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cantor</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Distribution support; not lead franchise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Needham</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Growth/technology distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Raymond James</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Retail and middle-market distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Societe Generale</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>European distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stifel</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Retail and growth distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>William Blair</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Growth-company distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BTG Pactual</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Latin America distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ING</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>European distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Macquarie Capital</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Asia-Pacific/infrastructure distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mirae Asset Securities</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Asia distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Mizuho</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Japan/global distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>European/Latin America distribution support.</t>
         </is>
       </c>
     </row>
@@ -1913,143 +1938,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>group_or_company</t>
+          <t>segment</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>revenue_2025_usd_b</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>operating_income_2025_usd_b</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda_2025_usd_b</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capex_2025_usd_b</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>revenue_q1_2026_usd_b</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>operating_income_q1_2026_usd_b</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda_q1_2026_usd_b</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>capex_q1_2026_usd_b</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>business_quality_score</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>operating_margin_2025_pct</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>capex_to_revenue_2025_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Small IPOs</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Below $5B IPO market cap or below $500M proceeds.</t>
-        </is>
+          <t>Space</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4.086</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.657</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.832</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.662</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.351</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Launch cadence and vertical integration are elite; still loss-making in Q1 and Starship execution is key.</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>-16.07929515418502</v>
+      </c>
+      <c r="M2" t="n">
+        <v>93.78365149290261</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SPACs/de-SPACs</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Different incentives, redemption mechanics and sponsor economics.</t>
-        </is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11.387</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4.423</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7.168</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.178</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.257</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.087</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.332</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Best current business: 2025 operating margin 38.8%, subscribers 8.9M at year-end and 10.3M Q1 2026; ARPU declining from $99 in 2023 to $66 Q1 2026.</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>38.84253973829806</v>
+      </c>
+      <c r="M3" t="n">
+        <v>36.69096337929217</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Biotech binary names</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Clinical-binary risk is not comparable to SpaceX.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Firefly Aerospace</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Context only</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Useful space-sector context, not a SpaceX-scale valuation or liquidity comp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Excluded from core</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Passes size floor but retail/social-media profile would overweight meme-demand mechanics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Instacart</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Excluded from core</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Not small by market cap, but lower-quality business comparability and smaller offering.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Context only</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Large direct listing, but no primary proceeds and no lead-underwriter execution.</t>
-        </is>
+          <t>AI/xAI/X</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.201</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-6.355</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.237</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12.727</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-2.469</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.609</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7.723</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Biggest upside and biggest quality penalty: $12.7B 2025 capex, large operating losses, related-party and regulatory complexity; Anthropic/Google contracts improve revenue visibility but are terminable.</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>-198.5317088409872</v>
+      </c>
+      <c r="M4" t="n">
+        <v>397.5945017182131</v>
       </c>
     </row>
   </sheetData>
@@ -2063,294 +2154,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>case</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>rule_area</t>
+          <t>revenue_usd_b</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>implied_market_cap_usd_b</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>spacex_read</t>
+          <t>price_to_sales_x</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>first_6m_model_impact</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Fast Entry</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>IPO can skip the normal three-full-calendar-month seasoning rule if its Full Market Capitalization ranks within the top 40 current Nasdaq-100 constituents. It is evaluated after the 7th trading day and typically added after 15 trading days, with announcement after the 10th trading day.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Likely eligible if SPCX lists on an eligible Nasdaq market and no final filing changes the share count. At $1.77T basic market cap, the top-40 size test should not be the gating item.</t>
-        </is>
+          <t>2025 reported revenue</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>18.674</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1765.241798625</v>
+      </c>
+      <c r="D2" t="n">
+        <v>94.52938838090392</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Creates a near-term QQQ/NDX flow catalyst around late June to early July 2026, not a day-one inclusion.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Nasdaq-100 Index Methodology</t>
+          <t>Contract run-rate cases are not risk-adjusted; Anthropic/Google contracts are terminable and delivery-dependent.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Liquidity</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Standard liquidity screen is three-month ADVT of at least $5M. For IPO fast entry, ADVT is measured from first trading day through the applicable reference date.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>A $75B IPO should almost certainly clear $5M ADVT, but this cannot be final until trading occurs.</t>
-        </is>
+          <t>Q1 2026 annualized</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>18.776</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1765.241798625</v>
+      </c>
+      <c r="D3" t="n">
+        <v>94.01586059996804</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Liquidity is a check-the-box risk, not the main risk.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Nasdaq-100 Index Methodology</t>
+          <t>Contract run-rate cases are not risk-adjusted; Anthropic/Google contracts are terminable and delivery-dependent.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Free float</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>No minimum free-float criterion. For low-float securities, index weighting uses the lesser of reported TSO or 3x free-floating shares.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Base IPO float is 555.6M shares, or 4.25% of basic shares. Initial NDX modified market cap is about $225.0B, not the full $1765.2B company value.</t>
-        </is>
+          <t>2025 revenue + Anthropic annualized run-rate</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>33.674</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1765.241798625</v>
+      </c>
+      <c r="D4" t="n">
+        <v>52.42150616573617</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The rule allows inclusion but scales the starting weight to tradable supply. This reduces, but does not eliminate, forced-buy pressure.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Nasdaq-100 Index Methodology</t>
+          <t>Contract run-rate cases are not risk-adjusted; Anthropic/Google contracts are terminable and delivery-dependent.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Quarterly path</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>The updated framework adds rank-based quarterly reviews in March, June and September, plus the annual December reconstitution.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>If fast entry were missed for an operational reason, the next scheduled framework matters. The first quarterly rebalance under the new rules is June 22, 2026.</t>
-        </is>
+          <t>2025 revenue + Anthropic + Google annualized run-rate</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>44.714</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1765.241798625</v>
+      </c>
+      <c r="D5" t="n">
+        <v>39.47850334626738</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Index demand can arrive in tranches rather than only at December reconstitution.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Nasdaq methodology update</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Seasoning</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>IPOs should trade on an eligible exchange for at least 12 months before consideration for S&amp;P Composite 1500 inclusion. No IPO fast track is allowed for S&amp;P Composite 1500 candidates.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Assuming first trade on June 12, 2026, the earliest simple seasoning date is June 12, 2027. This is only a possible consideration date, not an inclusion guarantee.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>No S&amp;P 500 forced-buy catalyst in the first six months.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>S&amp;P U.S. Indices Methodology; S&amp;P MegaCap consultation results</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Financial viability</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>GAAP net income from continuing operations must be positive for the most recent quarter and for the sum of the most recent four consecutive quarters.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SpaceX reported a 2025 net loss and a Q1 2026 net loss. It does not currently clear the profitability screen.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Even after 12 months, S&amp;P 500 inclusion likely requires a demonstrated profit turn.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>S&amp;P U.S. Indices Methodology; S&amp;P MegaCap consultation results</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Float and liquidity</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>S&amp;P Composite 1500 additions require IWF of at least 0.10, security-level FMC of at least 50% of the index market-cap threshold, FALR of at least 0.75, and at least 250,000 shares traded in each of the six months before evaluation.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Base IPO float is only 4.25% of basic shares, below the 10% IWF screen if only IPO shares count. Lock-up releases could change this later.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Float unlocks matter for S&amp;P eligibility, but they also create supply risk.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>S&amp;P U.S. Indices Methodology; S&amp;P MegaCap consultation results</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>S&amp;P Total Market / Dow Jones U.S. Total Stock Market</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Mega-cap broad-index update</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Effective June 8, 2026, broad-market indices allow an alternative IWF path for mega-cap companies and preserve IPO fast-track treatment when all other criteria are met.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Base float-adjusted market cap is about $75.0B, so broad-index eligibility may arrive much earlier than S&amp;P 500 eligibility.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Potential total-market ETF flow is relevant, but it should not be confused with S&amp;P 500 membership.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>S&amp;P MegaCap consultation results</t>
+          <t>Contract run-rate cases are not risk-adjusted; Anthropic/Google contracts are terminable and delivery-dependent.</t>
         </is>
       </c>
     </row>
@@ -2365,160 +2279,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>group_or_company</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>treatment</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>model_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>note</t>
+          <t>reason</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>First trade assumption</t>
+          <t>Small IPOs</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SPCX begins trading</t>
+          <t>Excluded</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Assumption based on June 2026 launch timing; update once 424B4/final exchange notice is filed.</t>
+          <t>Below $5B IPO market cap or below $500M proceeds.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nasdaq-100 IPO reference date</t>
+          <t>SPACs/de-SPACs</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7th trading day evaluation</t>
+          <t>Excluded</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Full market cap top-40 test and fast-entry eligibility check.</t>
+          <t>Different incentives, redemption mechanics and sponsor economics.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nasdaq-100 announcement window</t>
+          <t>Biotech binary names</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10th trading day announcement</t>
+          <t>Excluded</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Methodology says announcement typically occurs after close on the 10th trading day.</t>
+          <t>Clinical-binary risk is not comparable to SpaceX.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nasdaq-100 addition window</t>
+          <t>Firefly Aerospace</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15th trading day typical addition</t>
+          <t>Context only</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Methodology says IPO fast-entry addition typically occurs after 15 trading days; effective date can depend on notice conventions.</t>
+          <t>Useful space-sector context, not a SpaceX-scale valuation or liquidity comp.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S&amp;P broad-index fast-track</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S&amp;P TMI / Dow Jones TSM possible fast-track</t>
+          <t>Excluded from core</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Depends on S&amp;P DJI announcement and all applicable criteria; this is not S&amp;P 500.</t>
+          <t>Passes size floor but retail/social-media profile would overweight meme-demand mechanics.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S&amp;P 500 earliest seasoning date</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12 months after first trade</t>
+          <t>Excluded from core</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2027-06-12</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Only a possible consideration date. Profitability, IWF, liquidity and committee selection still apply.</t>
+          <t>Not small by market cap, but lower-quality business comparability and smaller offering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Large direct listing, but no primary proceeds and no lead-underwriter execution.</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2429,477 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>rule_area</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>spacex_read</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>first_6m_model_impact</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fast Entry</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IPO can skip the normal three-full-calendar-month seasoning rule if its Full Market Capitalization ranks within the top 40 current Nasdaq-100 constituents. It is evaluated after the 7th trading day and typically added after 15 trading days, with announcement after the 10th trading day.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Likely eligible if SPCX lists on an eligible Nasdaq market and no final filing changes the share count. At $1.77T basic market cap, the top-40 size test should not be the gating item.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Creates a near-term QQQ/NDX flow catalyst around late June to early July 2026, not a day-one inclusion.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nasdaq-100 Index Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Liquidity</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Standard liquidity screen is three-month ADVT of at least $5M. For IPO fast entry, ADVT is measured from first trading day through the applicable reference date.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A $75B IPO should almost certainly clear $5M ADVT, but this cannot be final until trading occurs.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Liquidity is a check-the-box risk, not the main risk.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nasdaq-100 Index Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Free float</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>No minimum free-float criterion. For low-float securities, index weighting uses the lesser of reported TSO or 3x free-floating shares.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Base IPO float is 555.6M shares, or 4.25% of basic shares. Initial NDX modified market cap is about $225.0B, not the full $1765.2B company value.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>The rule allows inclusion but scales the starting weight to tradable supply. This reduces, but does not eliminate, forced-buy pressure.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nasdaq-100 Index Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Quarterly path</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>The updated framework adds rank-based quarterly reviews in March, June and September, plus the annual December reconstitution.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>If fast entry were missed for an operational reason, the next scheduled framework matters. The first quarterly rebalance under the new rules is June 22, 2026.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Index demand can arrive in tranches rather than only at December reconstitution.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nasdaq methodology update</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Seasoning</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>IPOs should trade on an eligible exchange for at least 12 months before consideration for S&amp;P Composite 1500 inclusion. No IPO fast track is allowed for S&amp;P Composite 1500 candidates.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Assuming first trade on June 12, 2026, the earliest simple seasoning date is June 12, 2027. This is only a possible consideration date, not an inclusion guarantee.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>No S&amp;P 500 forced-buy catalyst in the first six months.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>S&amp;P U.S. Indices Methodology; S&amp;P MegaCap consultation results</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Financial viability</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GAAP net income from continuing operations must be positive for the most recent quarter and for the sum of the most recent four consecutive quarters.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SpaceX reported a 2025 net loss and a Q1 2026 net loss. It does not currently clear the profitability screen.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Even after 12 months, S&amp;P 500 inclusion likely requires a demonstrated profit turn.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>S&amp;P U.S. Indices Methodology; S&amp;P MegaCap consultation results</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Float and liquidity</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>S&amp;P Composite 1500 additions require IWF of at least 0.10, security-level FMC of at least 50% of the index market-cap threshold, FALR of at least 0.75, and at least 250,000 shares traded in each of the six months before evaluation.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Base IPO float is only 4.25% of basic shares, below the 10% IWF screen if only IPO shares count. Lock-up releases could change this later.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Float unlocks matter for S&amp;P eligibility, but they also create supply risk.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>S&amp;P U.S. Indices Methodology; S&amp;P MegaCap consultation results</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S&amp;P Total Market / Dow Jones U.S. Total Stock Market</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mega-cap broad-index update</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Effective June 8, 2026, broad-market indices allow an alternative IWF path for mega-cap companies and preserve IPO fast-track treatment when all other criteria are met.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Base float-adjusted market cap is about $75.0B, so broad-index eligibility may arrive much earlier than S&amp;P 500 eligibility.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Potential total-market ETF flow is relevant, but it should not be confused with S&amp;P 500 membership.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>S&amp;P MegaCap consultation results</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>model_date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>First trade assumption</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SPCX begins trading</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Assumption based on June 2026 launch timing; update once 424B4/final exchange notice is filed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nasdaq-100 IPO reference date</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7th trading day evaluation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Full market cap top-40 test and fast-entry eligibility check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nasdaq-100 announcement window</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10th trading day announcement</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Methodology says announcement typically occurs after close on the 10th trading day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nasdaq-100 addition window</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>15th trading day typical addition</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Methodology says IPO fast-entry addition typically occurs after 15 trading days; effective date can depend on notice conventions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S&amp;P broad-index fast-track</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S&amp;P TMI / Dow Jones TSM possible fast-track</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Depends on S&amp;P DJI announcement and all applicable criteria; this is not S&amp;P 500.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 earliest seasoning date</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12 months after first trade</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2027-06-12</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Only a possible consideration date. Profitability, IWF, liquidity and committee selection still apply.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2613,7 +2979,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IPO float scarcity can support the tape, but unlock waves are multiples of IPO float.</t>
+          <t>IPO float scarcity can support the tape, but cumulative tradable supply reaches about 9.4x IPO float by day 180 in both release scenarios.</t>
         </is>
       </c>
     </row>
@@ -2638,6 +3004,18 @@
       <c r="B11" t="inlineStr">
         <is>
           <t>No mega-cap fast track: 12-month IPO seasoning, positive GAAP income screens and IWF/liquidity screens remain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Day-180 lock-up ratio</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Performance case: 5.23B shares / 9.42x IPO float / 40.0% of basic shares. No-performance case: 5.25B shares / 9.44x / 40.1%.</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3582,6 +3960,26 @@
           <t>inside_first_6_months</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>release_x_base_ipo_float</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>release_pct_basic_common</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>release_pct_post_class_a</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>release_pct_relevant_pool</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -3621,6 +4019,16 @@
       <c r="I2" t="b">
         <v>1</v>
       </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.248709722567172</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7.527652199187732</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3660,6 +4068,16 @@
       <c r="I3" t="b">
         <v>1</v>
       </c>
+      <c r="J3" t="n">
+        <v>0.1499999995499999</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.6373064564731565</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.129147826490716</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3699,6 +4117,18 @@
       <c r="I4" t="b">
         <v>1</v>
       </c>
+      <c r="J4" t="n">
+        <v>1.6407000016407</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.970858048786818</v>
+      </c>
+      <c r="L4" t="n">
+        <v>12.35061897555793</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3738,6 +4168,18 @@
       <c r="I5" t="b">
         <v>1</v>
       </c>
+      <c r="J5" t="n">
+        <v>0.82044000082044</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.485811408268823</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6.17598697647757</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10.00109709270433</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3777,6 +4219,18 @@
       <c r="I6" t="b">
         <v>1</v>
       </c>
+      <c r="J6" t="n">
+        <v>0.5742000005742</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.43960912513768</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.322377897095973</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6.999451453647833</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3816,6 +4270,18 @@
       <c r="I7" t="b">
         <v>1</v>
       </c>
+      <c r="J7" t="n">
+        <v>0.5742000005742</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.43960912513768</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4.322377897095973</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6.999451453647833</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -3855,6 +4321,18 @@
       <c r="I8" t="b">
         <v>1</v>
       </c>
+      <c r="J8" t="n">
+        <v>0.10638000010638</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.4519777407386735</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.8007916417503825</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.296763576522216</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3894,6 +4372,18 @@
       <c r="I9" t="b">
         <v>1</v>
       </c>
+      <c r="J9" t="n">
+        <v>0.5911200005911199</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.511497293715404</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.449745772433598</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7.205704882062534</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3933,6 +4423,18 @@
       <c r="I10" t="b">
         <v>1</v>
       </c>
+      <c r="J10" t="n">
+        <v>0.5911200005911199</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.511497293715404</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.449745772433598</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7.205704882062534</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3972,6 +4474,18 @@
       <c r="I11" t="b">
         <v>1</v>
       </c>
+      <c r="J11" t="n">
+        <v>0.5911200005911199</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.511497293715404</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.449745772433598</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7.205704882062534</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4011,6 +4525,18 @@
       <c r="I12" t="b">
         <v>1</v>
       </c>
+      <c r="J12" t="n">
+        <v>2.34000000234</v>
+      </c>
+      <c r="K12" t="n">
+        <v>9.941980760749166</v>
+      </c>
+      <c r="L12" t="n">
+        <v>17.614706163714</v>
+      </c>
+      <c r="M12" t="n">
+        <v>28.52441031267142</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4050,6 +4576,18 @@
       <c r="I13" t="b">
         <v>1</v>
       </c>
+      <c r="J13" t="n">
+        <v>0.5911200005911199</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.511497293715404</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.449745772433598</v>
+      </c>
+      <c r="M13" t="n">
+        <v>7.205704882062534</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4089,6 +4627,18 @@
       <c r="I14" t="b">
         <v>1</v>
       </c>
+      <c r="J14" t="n">
+        <v>1.43568000143568</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6.099787580595026</v>
+      </c>
+      <c r="L14" t="n">
+        <v>10.80729972013714</v>
+      </c>
+      <c r="M14" t="n">
+        <v>17.50082281952825</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4128,6 +4678,18 @@
       <c r="I15" t="b">
         <v>0</v>
       </c>
+      <c r="J15" t="n">
+        <v>0.63342000063342</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.691217715159716</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4.768165460777658</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.4984375</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4167,6 +4729,18 @@
       <c r="I16" t="b">
         <v>0</v>
       </c>
+      <c r="J16" t="n">
+        <v>0.3168000003168</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.345991241455271</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.384760219087434</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.75</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4206,6 +4780,18 @@
       <c r="I17" t="b">
         <v>0</v>
       </c>
+      <c r="J17" t="n">
+        <v>0.63342000063342</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.691217715159716</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4.768165460777658</v>
+      </c>
+      <c r="M17" t="n">
+        <v>5.4984375</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4245,6 +4831,18 @@
       <c r="I18" t="b">
         <v>0</v>
       </c>
+      <c r="J18" t="n">
+        <v>0.3168000003168</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.345991241455271</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.384760219087434</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.75</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4284,6 +4882,18 @@
       <c r="I19" t="b">
         <v>0</v>
       </c>
+      <c r="J19" t="n">
+        <v>0.63342000063342</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.691217715159716</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4.768165460777658</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5.4984375</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4323,6 +4933,18 @@
       <c r="I20" t="b">
         <v>0</v>
       </c>
+      <c r="J20" t="n">
+        <v>11.52000001152</v>
+      </c>
+      <c r="K20" t="n">
+        <v>48.94513605291896</v>
+      </c>
+      <c r="L20" t="n">
+        <v>86.71855342136122</v>
+      </c>
+      <c r="M20" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4361,6 +4983,18 @@
       </c>
       <c r="I21" t="b">
         <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.63342000063342</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.691217715159716</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4.768165460777658</v>
+      </c>
+      <c r="M21" t="n">
+        <v>5.4984375</v>
       </c>
     </row>
   </sheetData>
@@ -4374,579 +5008,207 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ticker</t>
+          <t>pool</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>shares_m</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>inclusion_tier</t>
+          <t>x_base_ipo_float</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>management_quality</t>
+          <t>pct_basic_common</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>business_quality</t>
+          <t>pct_post_class_a</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ipo_quality</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>governance_quality</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>market_setup</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>weighted_quality_score</t>
+          <t>interpretation</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SPCX</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SpaceX</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Subject</t>
-        </is>
+          <t>Immediate IPO float</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>555.555555</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5</v>
+        <v>4.248709722567172</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Elite execution and underwriting; penalized for control, related parties, AI losses and unlock overhang.</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>3.625</v>
+        <v>7.527652199187732</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tradable at listing unless purchased by affiliates; this is the denominator for all unlock multiples.</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Core quality comp</t>
-        </is>
+          <t>Over-allotment option</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>83.333333</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1499999995499999</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5</v>
+        <v>0.633270582166067</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Best-in-class scaled network IPO; cleaner governance and profitability than SpaceX.</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>4.65</v>
+        <v>1.11654043444331</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Optional primary issuance, not a lock-up release. If exercised, immediate float rises to 638.9M shares.</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CRWD</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Core quality comp</t>
-        </is>
+          <t>180-day lock-up pool before affiliate timing</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4557.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8.2035000082035</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5</v>
+        <v>34.85429024393409</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Founder-led cybersecurity compounder with credible underwriting and strong public-market quality.</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>4.225000000000001</v>
+        <v>61.75309487778965</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Approximate pool inferred from S-1/A release percentages; releases are staged across Q2 earnings, day 70, day 90, day 105, day 120, day 135, Q3 earnings and day 180.</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DDOG</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Datadog</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Core quality comp</t>
-        </is>
+          <t>Base float plus 180-day pool</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5113.055555</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9.2035000082035</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5</v>
+        <v>39.10299996650126</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>High-quality founder-led software IPO with good governance and durable growth.</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>4.225000000000001</v>
+        <v>69.28074707697738</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Approximate before the 59.1M affiliate catch-up timing line; this is the clean first-six-month supply scale.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ABNB</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Airbnb</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Core quality comp</t>
-        </is>
+          <t>Extended lock-up excluding Musk</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1759.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.1671000031671</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5</v>
+        <v>13.45608857579858</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Founder-led platform with brand quality and strong IPO execution; dual-class governance but less extreme than SpaceX.</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>4.25</v>
+        <v>23.84082730388829</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Post-180-day releases beginning around Q4 2026 earnings, excluding Musk.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Meta/Facebook</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Scale/control comp</t>
-        </is>
+          <t>Musk 366-day lock-up</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6400</v>
+      </c>
+      <c r="C7" t="n">
+        <v>11.52000001152</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>48.94513605291896</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Best scale and founder-control comp; weak early trading shows scarcity does not immunize valuation.</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>4.225</v>
+        <v>86.71855342136122</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Largest single overhang; no early release in the S-1/A lock-up schedule.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARM</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Arm</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Scale/control comp</t>
-        </is>
+          <t>All named lock-up overhang after IPO float</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>12717</v>
+      </c>
+      <c r="C8" t="n">
+        <v>22.8906000228906</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>97.25551487265164</v>
       </c>
       <c r="E8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>High-quality tech asset with parent-control overhang; useful float-scarcity comp.</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Uber</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Scale comp</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Large institutional IPO; useful caution on valuation and post-listing profitability questions.</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>3.725</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SNOW</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Valuation caution comp</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Great company, extreme valuation at IPO; useful for pop/fade and valuation discipline.</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>3.825</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DASH</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>DoorDash</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Valuation caution comp</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Founder-led but cyclically expensive IPO; useful first-6-month caution.</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>3.625</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RIVN</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Capital intensity caution comp</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Institutional-scale but capex-heavy story IPO; useful negative comp for AI/Starship capex risk.</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>2.875</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BABA</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Alibaba</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Liquidity-only comp</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Mega IPO liquidity comp; not a clean U.S. governance comp due ADR/China/VIE issues.</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>3.525</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Excluded from core</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Large liquid listing, but direct listing with no primary IPO proceeds or lead underwriter.</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>2.825</v>
+        <v>172.3124756030392</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Potential supply overhang, not expected sale volume. Some Class B shares would need conversion before Class A trading.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4960,873 +5222,764 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ticker</t>
+          <t>order</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ipo_date</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ipo_proceeds_usd_b</t>
+          <t>model_date_if_prospectus_2026_06_11</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ipo_market_cap_usd_b</t>
+          <t>incremental_perf_case_m</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>listing_type</t>
+          <t>incremental_perf_case_x_ipo_float</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>lead_underwriters</t>
+          <t>cumulative_perf_case_m</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>inclusion</t>
+          <t>cumulative_perf_case_x_ipo_float</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>rationale</t>
+          <t>cumulative_perf_case_pct_basic_common</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>approx_ipo_public_float_pct</t>
+          <t>cumulative_perf_case_pct_post_class_a</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>float_note</t>
+          <t>incremental_no_perf_case_m</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>incremental_no_perf_case_x_ipo_float</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>cumulative_no_perf_case_m</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>cumulative_no_perf_case_x_ipo_float</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>cumulative_no_perf_case_pct_basic_common</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>cumulative_no_perf_case_pct_post_class_a</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SPCX</t>
-        </is>
+      <c r="A2" t="n">
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>IPO float</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-12 expected trading</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>75</v>
+          <t>At offering</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>1765.7</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Goldman Sachs, Morgan Stanley; large global syndicate</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Subject</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Passes scale and underwriting; unique control and AI roll-up risk.</t>
-        </is>
+        <v>555.555555</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>555.555555</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.248709722567172</v>
       </c>
       <c r="J2" t="n">
+        <v>7.527652199187732</v>
+      </c>
+      <c r="K2" t="n">
+        <v>555.555555</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>555.555555</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
         <v>4.248709722567172</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Calculated from S-1/A base IPO shares / post-offering basic shares.</t>
+      <c r="P2" t="n">
+        <v>7.527652199187732</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Starting tradable Class A supply.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>First earnings release unlock</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2008-03-19</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>17.9</v>
+          <t>Q2 2026 earnings window</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TBD - likely Aug 2026</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>J.P. Morgan, Goldman Sachs, BofA</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Large, profitable, high-quality operating company.</t>
-        </is>
+        <v>911.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.6407000016407</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1467.055555</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.6407000016407</v>
+      </c>
+      <c r="I3" t="n">
+        <v>11.21956777135399</v>
       </c>
       <c r="J3" t="n">
-        <v>42.61904761904762</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        <v>19.87827117474566</v>
+      </c>
+      <c r="K3" t="n">
+        <v>911.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.6407000016407</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1467.055555</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.6407000016407</v>
+      </c>
+      <c r="O3" t="n">
+        <v>11.21956777135399</v>
+      </c>
+      <c r="P3" t="n">
+        <v>19.87827117474566</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>20% release from 180-day pool.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
+      <c r="A4" t="n">
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Meta/Facebook</t>
+          <t>Performance early release</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2012-05-18</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>16</v>
+          <t>Q2 2026 earnings window</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TBD - likely Aug 2026</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>104</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Morgan Stanley, J.P. Morgan, Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Founder-control and mega-liquidity comp.</t>
-        </is>
+        <v>455.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.82044000082044</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1922.855555</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.46114000246114</v>
+      </c>
+      <c r="I4" t="n">
+        <v>14.70537917962281</v>
       </c>
       <c r="J4" t="n">
-        <v>15.38461538461538</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        <v>26.05425815122323</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1467.055555</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.6407000016407</v>
+      </c>
+      <c r="O4" t="n">
+        <v>11.21956777135399</v>
+      </c>
+      <c r="P4" t="n">
+        <v>19.87827117474566</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Only in performance case: price at least 30% above IPO price for 5 of 10 trading days.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BABA</t>
-        </is>
+      <c r="A5" t="n">
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Day 70 release</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>21.8</v>
+          <t>70th day after prospectus</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>168</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Primary IPO / ADR</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Credit Suisse, Deutsche Bank, Goldman Sachs, J.P. Morgan, Morgan Stanley, Citi</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Scale only</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Largest historical IPO comp; governance/geography not clean.</t>
-        </is>
+        <v>319</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5742000005742</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2241.855555</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.03534000303534</v>
+      </c>
+      <c r="I5" t="n">
+        <v>17.1449883047605</v>
       </c>
       <c r="J5" t="n">
-        <v>12.97619047619048</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        <v>30.37663604831921</v>
+      </c>
+      <c r="K5" t="n">
+        <v>319</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5742000005742</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1786.055555</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.2149000022149</v>
+      </c>
+      <c r="O5" t="n">
+        <v>13.65917689649167</v>
+      </c>
+      <c r="P5" t="n">
+        <v>24.20064907184164</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>7% release from 180-day pool.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
+      <c r="A6" t="n">
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Day 90 release</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2019-05-10</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>8.1</v>
+          <t>90th day after prospectus</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Morgan Stanley, Goldman Sachs, BofA</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Large growth IPO with profitability debate.</t>
-        </is>
+        <v>319</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5742000005742</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2560.855555</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.60954000360954</v>
+      </c>
+      <c r="I6" t="n">
+        <v>19.58459742989817</v>
       </c>
       <c r="J6" t="n">
-        <v>10.72847682119205</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        <v>34.69901394541518</v>
+      </c>
+      <c r="K6" t="n">
+        <v>319</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5742000005742</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2105.055555</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.789100002789099</v>
+      </c>
+      <c r="O6" t="n">
+        <v>16.09878602162935</v>
+      </c>
+      <c r="P6" t="n">
+        <v>28.52302696893761</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>7% release from 180-day pool.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ABNB</t>
-        </is>
+      <c r="A7" t="n">
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Affiliate catch-up release</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2020-12-10</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>3.5</v>
+          <t>91st day after prospectus</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>47</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Morgan Stanley, Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Founder-led platform quality comp.</t>
-        </is>
+        <v>59.1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.10638000010638</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2619.955555</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.71592000371592</v>
+      </c>
+      <c r="I7" t="n">
+        <v>20.03657517063685</v>
       </c>
       <c r="J7" t="n">
-        <v>7.446808510638298</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        <v>35.49980558716556</v>
+      </c>
+      <c r="K7" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.10638000010638</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2164.155555</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.895480002895479</v>
+      </c>
+      <c r="O7" t="n">
+        <v>16.55076376236802</v>
+      </c>
+      <c r="P7" t="n">
+        <v>29.32381861068799</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Rule 144 timing catch-up; shown as incremental tradable supply, not a new percentage tranche.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ARM</t>
-        </is>
+      <c r="A8" t="n">
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arm</t>
+          <t>Day 105 release</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>4.9</v>
+          <t>105th day after prospectus</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Barclays, Goldman Sachs, J.P. Morgan, Mizuho</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>High-quality controlled-company float-scarcity comp.</t>
-        </is>
+        <v>328.4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5911200005911199</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2948.355555</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.30704000430704</v>
+      </c>
+      <c r="I8" t="n">
+        <v>22.54807246435225</v>
       </c>
       <c r="J8" t="n">
-        <v>8.990825688073395</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        <v>39.94955135959916</v>
+      </c>
+      <c r="K8" t="n">
+        <v>328.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5911200005911199</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2492.555555</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.4866000034866</v>
+      </c>
+      <c r="O8" t="n">
+        <v>19.06226105608343</v>
+      </c>
+      <c r="P8" t="n">
+        <v>33.77356438312159</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>7% release from 180-day pool.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SNOW</t>
-        </is>
+      <c r="A9" t="n">
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Day 120 release</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>3.4</v>
+          <t>120th day after prospectus</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Goldman Sachs, Morgan Stanley, J.P. Morgan</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Quality company, valuation-risk comp.</t>
-        </is>
+        <v>328.4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5911200005911199</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3276.755555</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.89816000489816</v>
+      </c>
+      <c r="I9" t="n">
+        <v>25.05956975806766</v>
       </c>
       <c r="J9" t="n">
-        <v>10.3030303030303</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        <v>44.39929713203277</v>
+      </c>
+      <c r="K9" t="n">
+        <v>328.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5911200005911199</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2820.955555</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.07772000407772</v>
+      </c>
+      <c r="O9" t="n">
+        <v>21.57375834979883</v>
+      </c>
+      <c r="P9" t="n">
+        <v>38.22331015555518</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>7% release from 180-day pool.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DASH</t>
-        </is>
+      <c r="A10" t="n">
+        <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Day 135 release</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2020-12-09</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>3.4</v>
+          <t>135th day after prospectus</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
       </c>
       <c r="E10" t="n">
-        <v>39</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Goldman Sachs, J.P. Morgan</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Founder-led but valuation-sensitive growth IPO.</t>
-        </is>
+        <v>328.4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5911200005911199</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3605.155555</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.48928000548928</v>
+      </c>
+      <c r="I10" t="n">
+        <v>27.57106705178306</v>
       </c>
       <c r="J10" t="n">
-        <v>8.717948717948717</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        <v>48.84904290446636</v>
+      </c>
+      <c r="K10" t="n">
+        <v>328.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5911200005911199</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3149.355555</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5.66884000466884</v>
+      </c>
+      <c r="O10" t="n">
+        <v>24.08525564351424</v>
+      </c>
+      <c r="P10" t="n">
+        <v>42.67305592798878</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>7% release from 180-day pool.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RIVN</t>
-        </is>
+      <c r="A11" t="n">
+        <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Q3 2026 earnings release unlock</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.9</v>
+          <t>Q3 2026 earnings window</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TBD - likely Nov 2026</t>
+        </is>
       </c>
       <c r="E11" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Morgan Stanley, Goldman Sachs, J.P. Morgan</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Capital-intensity and story-stock caution comp.</t>
-        </is>
+        <v>1300</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.34000000234</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4905.155555</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8.829280007829279</v>
+      </c>
+      <c r="I11" t="n">
+        <v>37.51304781253222</v>
       </c>
       <c r="J11" t="n">
-        <v>17.89473684210526</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        <v>66.46374906818036</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.34000000234</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4449.355555</v>
+      </c>
+      <c r="N11" t="n">
+        <v>8.008840007008839</v>
+      </c>
+      <c r="O11" t="n">
+        <v>34.0272364042634</v>
+      </c>
+      <c r="P11" t="n">
+        <v>60.28776209170279</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>28% release from 180-day pool.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CRWD</t>
-        </is>
+      <c r="A12" t="n">
+        <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Day 180 final release</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.6</v>
+          <t>180th day after prospectus</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
       </c>
       <c r="E12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Goldman Sachs, J.P. Morgan, BofA, Barclays</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Passes lower bound; high-quality software/security comp.</t>
-        </is>
+        <v>328.4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5911200005911199</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5233.555555</v>
+      </c>
+      <c r="H12" t="n">
+        <v>9.420400008420399</v>
+      </c>
+      <c r="I12" t="n">
+        <v>40.02454510624763</v>
       </c>
       <c r="J12" t="n">
-        <v>8.823529411764707</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DDOG</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Datadog</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2019-09-19</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Morgan Stanley, Goldman Sachs, J.P. Morgan</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Passes lower bound; high-quality software/infrastructure comp.</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>7.692307692307693</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2021-04-14</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Direct listing</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Excluded from core</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Useful retail/liquidity context, but no primary IPO proceeds or underwriting comp.</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>RDDT</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2024-03-21</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Morgan Stanley, Goldman Sachs, J.P. Morgan</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Passes market-cap floor but too retail/social-media specific for SpaceX core comp.</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>11.71875</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CAVA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Cava</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>J.P. Morgan, Jefferies, Citi</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Below $5B IPO market-cap filter.</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CART</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Instacart/Maplebear</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2023-09-19</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E17" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Goldman Sachs, J.P. Morgan</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Weaker business-quality comparability and smaller offering.</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>6.666666666666667</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        <v>70.91349484061395</v>
+      </c>
+      <c r="K12" t="n">
+        <v>797.6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.43568000143568</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5246.955555</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9.44452000844452</v>
+      </c>
+      <c r="O12" t="n">
+        <v>40.12702398485843</v>
+      </c>
+      <c r="P12" t="n">
+        <v>71.09506181183993</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Final 180-day release is smaller if the performance release happened, larger if it did not.</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5852,166 +6005,208 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>first_trade_date</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>first_close_adj_usd</t>
+          <t>inclusion_tier</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>return_from_first_close_1d_pct</t>
+          <t>management_quality</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>return_from_first_close_1m_pct</t>
+          <t>business_quality</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>return_from_first_close_3m_pct</t>
+          <t>ipo_quality</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>return_from_first_close_6m_pct</t>
+          <t>governance_quality</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>market_setup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_quality_score</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2012-05-18</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>37.93</v>
+          <t>SpaceX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>-11</v>
+        <v>4.5</v>
       </c>
       <c r="E2" t="n">
-        <v>-16.5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>-50.2</v>
+        <v>4.5</v>
       </c>
       <c r="G2" t="n">
-        <v>-40</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
-        </is>
+        <v>1.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Elite execution and underwriting; penalized for control, related parties, AI losses and unlock overhang.</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>3.625</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>89.17</v>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Core quality comp</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>-4.3</v>
+        <v>4.5</v>
       </c>
       <c r="E3" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>16.4</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Best-in-class scaled network IPO; cleaner governance and profitability than SpaceX.</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>4.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2008-03-19</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>12.42</v>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Core quality comp</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>4.5</v>
       </c>
       <c r="E4" t="n">
-        <v>22.1</v>
+        <v>4.5</v>
       </c>
       <c r="F4" t="n">
-        <v>48.4</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Founder-led cybersecurity compounder with credible underwriting and strong public-market quality.</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>4.225000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2019-05-10</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>41.57</v>
+          <t>Datadog</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Core quality comp</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>-10.8</v>
+        <v>4.5</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.7</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>-34.1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>High-quality founder-led software IPO with good governance and durable growth.</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>4.225000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -6022,220 +6217,356 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2020-12-10</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>144.71</v>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Core quality comp</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>-3.8</v>
+        <v>4.5</v>
       </c>
       <c r="E6" t="n">
-        <v>11.1</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="n">
-        <v>45.1</v>
+        <v>4.5</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
-        </is>
+        <v>3.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Founder-led platform with brand quality and strong IPO execution; dual-class governance but less extreme than SpaceX.</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>63.59</v>
+          <t>Meta/Facebook</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Scale/control comp</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>-4.5</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>-20.1</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
-        </is>
+        <v>2.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Best scale and founder-control comp; weak early trading shows scarcity does not immunize valuation.</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>4.225</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>253.93</v>
+          <t>Arm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Scale/control comp</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>-10.4</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.1</v>
+        <v>4.5</v>
       </c>
       <c r="F8" t="n">
-        <v>29.4</v>
+        <v>4.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-14.7</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
-        </is>
+        <v>2.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>High-quality tech asset with parent-control overhang; useful float-scarcity comp.</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2020-12-09</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>189.51</v>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Scale comp</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.9</v>
+        <v>3.5</v>
       </c>
       <c r="E9" t="n">
-        <v>-11.9</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>-25.1</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>-18.7</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
-        </is>
+        <v>3.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Large institutional IPO; useful caution on valuation and post-listing profitability questions.</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>3.725</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RIVN</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>100.73</v>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Valuation caution comp</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>22.1</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>13.8</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>-35.7</v>
+        <v>4.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-75.90000000000001</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
-        </is>
+        <v>3.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Great company, extreme valuation at IPO; useful for pop/fade and valuation discipline.</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>3.825</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>58</v>
+          <t>DoorDash</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Valuation caution comp</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>16.5</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>26.7</v>
+        <v>3.5</v>
       </c>
       <c r="F11" t="n">
-        <v>19.2</v>
+        <v>4.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-18</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Founder-led but cyclically expensive IPO; useful first-6-month caution.</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>3.625</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>RIVN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2019-09-19</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>37.55</v>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Capital intensity caution comp</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>-3.7</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>-15.9</v>
+        <v>2.5</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>-11.1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Institutional-scale but capex-heavy story IPO; useful negative comp for AI/Starship capex risk.</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>2.875</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BABA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Alibaba</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Liquidity-only comp</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Mega IPO liquidity comp; not a clean U.S. governance comp due ADR/China/VIE issues.</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3.525</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Excluded from core</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Large liquid listing, but direct listing with no primary IPO proceeds or lead underwriter.</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>2.825</v>
       </c>
     </row>
   </sheetData>
@@ -6249,160 +6580,873 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>horizon_days</t>
+          <t>ticker</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>positive_pct</t>
+          <t>ipo_date</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>median_abs_return_pct</t>
+          <t>ipo_proceeds_usd_b</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mean_abs_return_pct</t>
+          <t>ipo_market_cap_usd_b</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>median_excess_vs_spy_pct</t>
+          <t>listing_type</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>beat_spy_pct</t>
+          <t>lead_underwriters</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>inclusion</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>rationale</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>approx_ipo_public_float_pct</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>float_note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>30</v>
-      </c>
-      <c r="B2" t="n">
-        <v>760</v>
-      </c>
-      <c r="C2" t="n">
-        <v>53.2</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SpaceX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-06-12 expected trading</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>0.2</v>
+        <v>75</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="G2" t="n">
+        <v>1765.7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Goldman Sachs, Morgan Stanley; large global syndicate</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Passes scale and underwriting; unique control and AI roll-up risk.</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>4.248709722567172</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Calculated from S-1/A base IPO shares / post-offering basic shares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2008-03-19</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>J.P. Morgan, Goldman Sachs, BofA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Large, profitable, high-quality operating company.</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>42.61904761904762</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Meta/Facebook</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2012-05-18</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" t="n">
+        <v>104</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Morgan Stanley, J.P. Morgan, Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Founder-control and mega-liquidity comp.</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>15.38461538461538</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BABA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Alibaba</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2014-09-19</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>168</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Primary IPO / ADR</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Credit Suisse, Deutsche Bank, Goldman Sachs, J.P. Morgan, Morgan Stanley, Citi</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Scale only</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Largest historical IPO comp; governance/geography not clean.</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>12.97619047619048</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2019-05-10</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Morgan Stanley, Goldman Sachs, BofA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Large growth IPO with profitability debate.</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>10.72847682119205</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2020-12-10</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>47</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Morgan Stanley, Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Founder-led platform quality comp.</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>7.446808510638298</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Barclays, Goldman Sachs, J.P. Morgan, Mizuho</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>High-quality controlled-company float-scarcity comp.</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>8.990825688073395</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>33</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goldman Sachs, Morgan Stanley, J.P. Morgan</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Quality company, valuation-risk comp.</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>10.3030303030303</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DoorDash</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2020-12-09</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E10" t="n">
         <v>39</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>YehCapital study 15; day-1-close entries for 760 US IPOs since 2022-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>90</v>
-      </c>
-      <c r="B3" t="n">
-        <v>731</v>
-      </c>
-      <c r="C3" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="G3" t="n">
-        <v>29</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>YehCapital study 15; day-1-close entries for 760 US IPOs since 2022-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>180</v>
-      </c>
-      <c r="B4" t="n">
-        <v>641</v>
-      </c>
-      <c r="C4" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-11.3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-15.4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>25</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>YehCapital study 15; day-1-close entries for 760 US IPOs since 2022-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>365</v>
-      </c>
-      <c r="B5" t="n">
-        <v>474</v>
-      </c>
-      <c r="C5" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-16.2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-28.4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>19</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>YehCapital study 15; day-1-close entries for 760 US IPOs since 2022-10</t>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goldman Sachs, J.P. Morgan</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Founder-led but valuation-sensitive growth IPO.</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>8.717948717948717</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RIVN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Morgan Stanley, Goldman Sachs, J.P. Morgan</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Capital-intensity and story-stock caution comp.</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>17.89473684210526</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2019-06-12</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goldman Sachs, J.P. Morgan, BofA, Barclays</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Passes lower bound; high-quality software/security comp.</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>8.823529411764707</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DDOG</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Datadog</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2019-09-19</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Morgan Stanley, Goldman Sachs, J.P. Morgan</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Passes lower bound; high-quality software/infrastructure comp.</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2021-04-14</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Direct listing</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Excluded from core</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Useful retail/liquidity context, but no primary IPO proceeds or underwriting comp.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2024-03-21</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Morgan Stanley, Goldman Sachs, J.P. Morgan</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Passes market-cap floor but too retail/social-media specific for SpaceX core comp.</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>11.71875</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CAVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cava</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>J.P. Morgan, Jefferies, Citi</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Below $5B IPO market-cap filter.</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Instacart/Maplebear</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goldman Sachs, J.P. Morgan</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Weaker business-quality comparability and smaller offering.</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
         </is>
       </c>
     </row>
@@ -6417,41 +7461,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>sector</t>
+          <t>ticker</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>first_trade_date</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>positive_90d_pct</t>
+          <t>first_close_adj_usd</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>median_90d_return_pct</t>
+          <t>return_from_first_close_1d_pct</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>median_365d_return_pct</t>
+          <t>return_from_first_close_1m_pct</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>spacex_model_read</t>
+          <t>return_from_first_close_3m_pct</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>return_from_first_close_6m_pct</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -6460,145 +7509,352 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software / IT</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>30</v>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2012-05-18</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>65.5</v>
+        <v>37.93</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4</v>
+        <v>-11</v>
       </c>
       <c r="E2" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Survivor bucket in study 15; closest public-market analogue to profitable infrastructure/software quality.</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>YehCapital study 15 sector table</t>
+        <v>-16.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-50.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-40</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Real Estate / REIT</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>192</v>
+          <t>BABA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2014-09-19</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>79.8</v>
+        <v>89.17</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>-4.3</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Survivor bucket but not comparable to SpaceX business quality or capital cycle.</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>YehCapital study 15 sector table</t>
+        <v>-6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Biotech / Pharma</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>53</v>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2008-03-19</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>32.1</v>
+        <v>12.42</v>
       </c>
       <c r="D4" t="n">
-        <v>-13</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="n">
-        <v>-30.3</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Explicitly excluded from the SpaceX comp set.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>YehCapital study 15 sector table</t>
+        <v>22.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>21</v>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2019-05-10</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>47.4</v>
+        <v>41.57</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.7</v>
+        <v>-10.8</v>
       </c>
       <c r="E5" t="n">
-        <v>-63.4</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Too small/noisy as a broad bucket; not a mega-cap aerospace/space comp.</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>YehCapital study 15 sector table</t>
+        <v>2.1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-34.1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Micro-cap / unclassified</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>324</v>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2020-12-10</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>43.8</v>
+        <v>144.71</v>
       </c>
       <c r="D6" t="n">
-        <v>-8.300000000000001</v>
+        <v>-3.8</v>
       </c>
       <c r="E6" t="n">
-        <v>-63.7</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Explicitly excluded from the SpaceX comp set.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>YehCapital study 15 sector table</t>
+        <v>11.1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>63.59</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-20.1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>253.93</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2020-12-09</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>189.51</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-18.7</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RIVN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>100.73</v>
+      </c>
+      <c r="D10" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-35.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-75.90000000000001</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2019-06-12</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>58</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F11" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DDOG</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2019-09-19</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-15.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
         </is>
       </c>
     </row>

--- a/24-spacex-ipo-quality-model/spacex_ipo_quality_model.xlsx
+++ b/24-spacex-ipo-quality-model/spacex_ipo_quality_model.xlsx
@@ -13,19 +13,23 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lockup_calendar" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lockup_supply_summary" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lockup_first_6m_scenarios" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quality_scores" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="comp_universe" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="comp_ipo_performance" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ipo_chase_base_rate" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ipo_chase_sector_base_rate" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="combined_ipo_decision_bridge" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="underwriter_quality" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="segment_quality" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="valuation_sensitivity" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="excluded_comps" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="index_inclusion_rules" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="index_inclusion_timeline" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nasdaq_explainer" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spacex_business_breakdown" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spacex_ai_timeline" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cursor_option_analysis" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quality_scores" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="comp_universe" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="comp_ipo_performance" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ipo_chase_base_rate" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ipo_chase_sector_base_rate" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="combined_ipo_decision_bridge" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="underwriter_quality" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="segment_quality" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="valuation_sensitivity" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="excluded_comps" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="index_inclusion_rules" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="index_inclusion_timeline" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -969,160 +973,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>horizon_days</t>
+          <t>topic</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>answer</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>positive_pct</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>median_abs_return_pct</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mean_abs_return_pct</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>median_excess_vs_spy_pct</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>beat_spy_pct</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
+          <t>investor_read</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>30</v>
-      </c>
-      <c r="B2" t="n">
-        <v>760</v>
-      </c>
-      <c r="C2" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>YehCapital study 15; day-1-close entries for 760 US IPOs since 2022-10</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Not acquired as of S-1/A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SpaceX has a collaboration and option, not completed ownership of Cursor.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>90</v>
-      </c>
-      <c r="B3" t="n">
-        <v>731</v>
-      </c>
-      <c r="C3" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="G3" t="n">
-        <v>29</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>YehCapital study 15; day-1-close entries for 760 US IPOs since 2022-10</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Anysphere, Inc. doing business as Cursor</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Private software company focused on AI-assisted coding workflows.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>180</v>
-      </c>
-      <c r="B4" t="n">
-        <v>641</v>
-      </c>
-      <c r="C4" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-11.3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-15.4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>25</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>YehCapital study 15; day-1-close entries for 760 US IPOs since 2022-10</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Agreement date</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Compute and option agreement entered in April 2026.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>365</v>
-      </c>
-      <c r="B5" t="n">
-        <v>474</v>
-      </c>
-      <c r="C5" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-16.2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-28.4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>19</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>YehCapital study 15; day-1-close entries for 760 US IPOs since 2022-10</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Compute agreement</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SpaceX provides certain GPU cluster compute capacity</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cursor contributes personnel, data/datasets, documentation, technical know-how, workflows, prompts, specifications and code per FWP/S-1 disclosure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Right, not obligation, to acquire Cursor</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Consideration would be SpaceX Class A stock based on Cursor implied equity value of $60.0B and SpaceX VWAP before closing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Termination economics</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>$1.5B termination fee plus $8.5B deferred services fee if applicable</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fees payable in cash or Class A stock if the offering has not been consummated when payable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Investor read</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Strategic upside with dilution/complexity risk</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Cursor could add developer distribution and model-training data, but it is not current owned revenue and should not be valued as a completed acquisition.</t>
         </is>
       </c>
     </row>
@@ -1137,189 +1123,579 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>sector</t>
+          <t>ticker</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>positive_90d_pct</t>
+          <t>inclusion_tier</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>median_90d_return_pct</t>
+          <t>management_quality</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>median_365d_return_pct</t>
+          <t>business_quality</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>spacex_model_read</t>
+          <t>ipo_quality</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>governance_quality</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>market_setup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_quality_score</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software / IT</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>30</v>
-      </c>
-      <c r="C2" t="n">
-        <v>65.5</v>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SpaceX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="E2" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Survivor bucket in study 15; closest public-market analogue to profitable infrastructure/software quality.</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>YehCapital study 15 sector table</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Elite execution and underwriting; penalized for control, related parties, AI losses and unlock overhang.</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>3.625</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Real Estate / REIT</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>192</v>
-      </c>
-      <c r="C3" t="n">
-        <v>79.8</v>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Core quality comp</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Survivor bucket but not comparable to SpaceX business quality or capital cycle.</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>YehCapital study 15 sector table</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Best-in-class scaled network IPO; cleaner governance and profitability than SpaceX.</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>4.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Biotech / Pharma</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>53</v>
-      </c>
-      <c r="C4" t="n">
-        <v>32.1</v>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Core quality comp</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>-13</v>
+        <v>4.5</v>
       </c>
       <c r="E4" t="n">
-        <v>-30.3</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Explicitly excluded from the SpaceX comp set.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>YehCapital study 15 sector table</t>
-        </is>
+        <v>4.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Founder-led cybersecurity compounder with credible underwriting and strong public-market quality.</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>4.225000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>21</v>
-      </c>
-      <c r="C5" t="n">
-        <v>47.4</v>
+          <t>DDOG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Datadog</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Core quality comp</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>-4.7</v>
+        <v>4.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-63.4</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Too small/noisy as a broad bucket; not a mega-cap aerospace/space comp.</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>YehCapital study 15 sector table</t>
-        </is>
+        <v>4.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>High-quality founder-led software IPO with good governance and durable growth.</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>4.225000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Micro-cap / unclassified</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>324</v>
-      </c>
-      <c r="C6" t="n">
-        <v>43.8</v>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Core quality comp</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>-8.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-63.7</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Explicitly excluded from the SpaceX comp set.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>YehCapital study 15 sector table</t>
-        </is>
+        <v>4.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Founder-led platform with brand quality and strong IPO execution; dual-class governance but less extreme than SpaceX.</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Meta/Facebook</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Scale/control comp</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Best scale and founder-control comp; weak early trading shows scarcity does not immunize valuation.</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>4.225</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Scale/control comp</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>High-quality tech asset with parent-control overhang; useful float-scarcity comp.</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Scale comp</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Large institutional IPO; useful caution on valuation and post-listing profitability questions.</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>3.725</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Valuation caution comp</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Great company, extreme valuation at IPO; useful for pop/fade and valuation discipline.</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>3.825</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DoorDash</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Valuation caution comp</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Founder-led but cyclically expensive IPO; useful first-6-month caution.</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>3.625</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RIVN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Capital intensity caution comp</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Institutional-scale but capex-heavy story IPO; useful negative comp for AI/Starship capex risk.</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>2.875</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BABA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Alibaba</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Liquidity-only comp</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Mega IPO liquidity comp; not a clean U.S. governance comp due ADR/China/VIE issues.</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3.525</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Excluded from core</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Large liquid listing, but direct listing with no primary IPO proceeds or lead underwriter.</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>2.825</v>
       </c>
     </row>
   </sheetData>
@@ -1333,141 +1709,873 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>layer</t>
+          <t>ticker</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>finding</t>
+          <t>ipo_date</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>key_number</t>
+          <t>ipo_proceeds_usd_b</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>spacex_decision_rule</t>
+          <t>ipo_market_cap_usd_b</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>listing_type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>lead_underwriters</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>inclusion</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>rationale</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>approx_ipo_public_float_pct</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>float_note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Broad IPO prior</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Study 15</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Day-1-close IPO chasing is a negative base-rate trade.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>365d median excess vs SPY -28.4%; only 19% beat SPY.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Start from skepticism; do not buy SpaceX just because the IPO is famous.</t>
+          <t>2026-06-12 expected trading</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>75</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1765.7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Goldman Sachs, Morgan Stanley; large global syndicate</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Passes scale and underwriting; unique control and AI roll-up risk.</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>4.248709722567172</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Calculated from S-1/A base IPO shares / post-offering basic shares.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Quality filter</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Study 24</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Small/noisy IPOs are removed; only institutional-scale comps remain.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Filtered 6m comp median from first close -14.7%.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Quality filter reduces junk risk but still leaves post-IPO fade risk.</t>
+          <t>2008-03-19</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>J.P. Morgan, Goldman Sachs, BofA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Large, profitable, high-quality operating company.</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>42.61904761904762</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Scarcity and index flow</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 24</t>
+          <t>Meta/Facebook</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SpaceX has unusually tight immediate tradable supply plus a Nasdaq-100 fast-entry path.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Immediate float 4.25%; Nasdaq low-float modified market cap about $225B.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Treat early upside as flow/scarcity, not proof of long-term entry quality.</t>
+          <t>2012-05-18</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" t="n">
+        <v>104</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Morgan Stanley, J.P. Morgan, Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Founder-control and mega-liquidity comp.</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>15.38461538461538</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unlock and governance penalty</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Study 24</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>First-six-month releases, Musk control and registration-rights overhang cap public-entry quality.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Q2/Q3 earnings unlocks plus 70/90/105/120/135/180-day releases are multiples of IPO float.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Wait for unlock absorption before underwriting a larger long-term position.</t>
+          <t>2014-09-19</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>168</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Primary IPO / ADR</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Credit Suisse, Deutsche Bank, Goldman Sachs, J.P. Morgan, Morgan Stanley, Citi</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Scale only</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Largest historical IPO comp; governance/geography not clean.</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>12.97619047619048</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2019-05-10</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Morgan Stanley, Goldman Sachs, BofA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Large growth IPO with profitability debate.</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>10.72847682119205</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2020-12-10</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>47</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Morgan Stanley, Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Founder-led platform quality comp.</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>7.446808510638298</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Barclays, Goldman Sachs, J.P. Morgan, Mizuho</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>High-quality controlled-company float-scarcity comp.</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>8.990825688073395</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>33</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goldman Sachs, Morgan Stanley, J.P. Morgan</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Quality company, valuation-risk comp.</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>10.3030303030303</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DoorDash</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2020-12-09</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>39</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goldman Sachs, J.P. Morgan</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Founder-led but valuation-sensitive growth IPO.</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>8.717948717948717</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RIVN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Morgan Stanley, Goldman Sachs, J.P. Morgan</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Capital-intensity and story-stock caution comp.</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>17.89473684210526</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2019-06-12</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goldman Sachs, J.P. Morgan, BofA, Barclays</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Passes lower bound; high-quality software/security comp.</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>8.823529411764707</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DDOG</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Datadog</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2019-09-19</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Morgan Stanley, Goldman Sachs, J.P. Morgan</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Passes lower bound; high-quality software/infrastructure comp.</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2021-04-14</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Direct listing</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Excluded from core</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Useful retail/liquidity context, but no primary IPO proceeds or underwriting comp.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2024-03-21</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Morgan Stanley, Goldman Sachs, J.P. Morgan</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Passes market-cap floor but too retail/social-media specific for SpaceX core comp.</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>11.71875</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CAVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cava</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>J.P. Morgan, Jefferies, Citi</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Below $5B IPO market-cap filter.</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Instacart/Maplebear</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Primary IPO</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goldman Sachs, J.P. Morgan</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Weaker business-quality comparability and smaller offering.</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
         </is>
       </c>
     </row>
@@ -1482,448 +2590,400 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>underwriter</t>
+          <t>ticker</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>first_trade_date</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>quality_score</t>
+          <t>first_close_adj_usd</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>return_from_first_close_1d_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>return_from_first_close_1m_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>return_from_first_close_3m_pct</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>return_from_first_close_6m_pct</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Joint bookrunner / lead-left group</t>
+          <t>2012-05-18</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Top-tier mega-cap IPO franchise and stabilization credibility.</t>
+        <v>37.93</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-50.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-40</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Joint bookrunner / lead-left group</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Top-tier technology IPO franchise; stabilization agent per S-1/A.</t>
+        <v>89.17</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BofA Securities</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Joint bookrunner</t>
+          <t>2008-03-19</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Top global distribution and lending relationship.</t>
+        <v>12.42</v>
+      </c>
+      <c r="D4" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Joint bookrunner</t>
+          <t>2019-05-10</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Top global distribution; strong cross-border reach.</t>
+        <v>41.57</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-10.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-34.1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J.P. Morgan</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Joint bookrunner</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Top global equity capital markets franchise.</t>
+        <v>144.71</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Joint bookrunner</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Strong global technology/industrial ECM distribution.</t>
+        <v>63.59</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-20.1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deutsche Bank Securities</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Joint bookrunner</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Global bank; useful international distribution.</t>
+        <v>253.93</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wells Fargo Securities</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bookrunner</t>
+          <t>2020-12-09</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Large U.S. distribution and lending relationship.</t>
+        <v>189.51</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-18.7</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Allen &amp; Company</t>
+          <t>RIVN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bookrunner</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Elite tech/media relationship bank; narrower distribution.</t>
+        <v>100.73</v>
+      </c>
+      <c r="D10" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-35.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-75.90000000000001</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cantor</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bookrunner</t>
+          <t>2019-06-12</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Distribution support; not lead franchise.</t>
+        <v>58</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F11" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Needham</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bookrunner</t>
+          <t>2019-09-19</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Growth/technology distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Raymond James</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Retail and middle-market distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Societe Generale</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>European distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Stifel</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Retail and growth distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>William Blair</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Growth-company distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>BTG Pactual</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Latin America distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ING</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>European distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Macquarie Capital</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Asia-Pacific/infrastructure distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Mirae Asset Securities</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Asia distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Mizuho</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Japan/global distribution support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Bookrunner</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>European/Latin America distribution support.</t>
+        <v>37.55</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-15.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
         </is>
       </c>
     </row>
@@ -1938,209 +2998,161 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>segment</t>
+          <t>horizon_days</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>revenue_2025_usd_b</t>
+          <t>n</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>operating_income_2025_usd_b</t>
+          <t>positive_pct</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>adjusted_ebitda_2025_usd_b</t>
+          <t>median_abs_return_pct</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>capex_2025_usd_b</t>
+          <t>mean_abs_return_pct</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>revenue_q1_2026_usd_b</t>
+          <t>median_excess_vs_spy_pct</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>operating_income_q1_2026_usd_b</t>
+          <t>beat_spy_pct</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>adjusted_ebitda_q1_2026_usd_b</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>capex_q1_2026_usd_b</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>business_quality_score</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>operating_margin_2025_pct</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>capex_to_revenue_2025_pct</t>
+          <t>source</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
+      <c r="A2" t="n">
+        <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>4.086</v>
+        <v>760</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.657</v>
+        <v>53.2</v>
       </c>
       <c r="D2" t="n">
-        <v>0.653</v>
+        <v>0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>3.832</v>
+        <v>-2.1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.619</v>
+        <v>-1.9</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.662</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-0.351</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.052</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Launch cadence and vertical integration are elite; still loss-making in Q1 and Starship execution is key.</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>-16.07929515418502</v>
-      </c>
-      <c r="M2" t="n">
-        <v>93.78365149290261</v>
+        <v>39</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>YehCapital study 15; day-1-close entries for 760 US IPOs since 2022-10</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Connectivity</t>
-        </is>
+      <c r="A3" t="n">
+        <v>90</v>
       </c>
       <c r="B3" t="n">
-        <v>11.387</v>
+        <v>731</v>
       </c>
       <c r="C3" t="n">
-        <v>4.423</v>
+        <v>52.8</v>
       </c>
       <c r="D3" t="n">
-        <v>7.168</v>
+        <v>0.3</v>
       </c>
       <c r="E3" t="n">
-        <v>4.178</v>
+        <v>-1.6</v>
       </c>
       <c r="F3" t="n">
-        <v>3.257</v>
+        <v>-6.6</v>
       </c>
       <c r="G3" t="n">
-        <v>1.188</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.087</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.332</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Best current business: 2025 operating margin 38.8%, subscribers 8.9M at year-end and 10.3M Q1 2026; ARPU declining from $99 in 2023 to $66 Q1 2026.</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>38.84253973829806</v>
-      </c>
-      <c r="M3" t="n">
-        <v>36.69096337929217</v>
+        <v>29</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>YehCapital study 15; day-1-close entries for 760 US IPOs since 2022-10</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AI/xAI/X</t>
-        </is>
+      <c r="A4" t="n">
+        <v>180</v>
       </c>
       <c r="B4" t="n">
-        <v>3.201</v>
+        <v>641</v>
       </c>
       <c r="C4" t="n">
-        <v>-6.355</v>
+        <v>47.6</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.237</v>
+        <v>-1.1</v>
       </c>
       <c r="E4" t="n">
-        <v>12.727</v>
+        <v>-11.3</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8179999999999999</v>
+        <v>-15.4</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.469</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-0.609</v>
-      </c>
-      <c r="I4" t="n">
-        <v>7.723</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Biggest upside and biggest quality penalty: $12.7B 2025 capex, large operating losses, related-party and regulatory complexity; Anthropic/Google contracts improve revenue visibility but are terminable.</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>-198.5317088409872</v>
-      </c>
-      <c r="M4" t="n">
-        <v>397.5945017182131</v>
+        <v>25</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>YehCapital study 15; day-1-close entries for 760 US IPOs since 2022-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>365</v>
+      </c>
+      <c r="B5" t="n">
+        <v>474</v>
+      </c>
+      <c r="C5" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-28.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>19</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>YehCapital study 15; day-1-close entries for 760 US IPOs since 2022-10</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2154,117 +3166,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>case</t>
+          <t>sector</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>revenue_usd_b</t>
+          <t>n</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>implied_market_cap_usd_b</t>
+          <t>positive_90d_pct</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>price_to_sales_x</t>
+          <t>median_90d_return_pct</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>median_365d_return_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>spacex_model_read</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025 reported revenue</t>
+          <t>Software / IT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.674</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>1765.241798625</v>
+        <v>65.5</v>
       </c>
       <c r="D2" t="n">
-        <v>94.52938838090392</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Contract run-rate cases are not risk-adjusted; Anthropic/Google contracts are terminable and delivery-dependent.</t>
+        <v>3.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Survivor bucket in study 15; closest public-market analogue to profitable infrastructure/software quality.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>YehCapital study 15 sector table</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Q1 2026 annualized</t>
+          <t>Real Estate / REIT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.776</v>
+        <v>192</v>
       </c>
       <c r="C3" t="n">
-        <v>1765.241798625</v>
+        <v>79.8</v>
       </c>
       <c r="D3" t="n">
-        <v>94.01586059996804</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Contract run-rate cases are not risk-adjusted; Anthropic/Google contracts are terminable and delivery-dependent.</t>
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Survivor bucket but not comparable to SpaceX business quality or capital cycle.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>YehCapital study 15 sector table</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025 revenue + Anthropic annualized run-rate</t>
+          <t>Biotech / Pharma</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33.674</v>
+        <v>53</v>
       </c>
       <c r="C4" t="n">
-        <v>1765.241798625</v>
+        <v>32.1</v>
       </c>
       <c r="D4" t="n">
-        <v>52.42150616573617</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Contract run-rate cases are not risk-adjusted; Anthropic/Google contracts are terminable and delivery-dependent.</t>
+        <v>-13</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Explicitly excluded from the SpaceX comp set.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>YehCapital study 15 sector table</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025 revenue + Anthropic + Google annualized run-rate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44.714</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>1765.241798625</v>
+        <v>47.4</v>
       </c>
       <c r="D5" t="n">
-        <v>39.47850334626738</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Contract run-rate cases are not risk-adjusted; Anthropic/Google contracts are terminable and delivery-dependent.</t>
+        <v>-4.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-63.4</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Too small/noisy as a broad bucket; not a mega-cap aerospace/space comp.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>YehCapital study 15 sector table</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Micro-cap / unclassified</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>324</v>
+      </c>
+      <c r="C6" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-63.7</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Explicitly excluded from the SpaceX comp set.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>YehCapital study 15 sector table</t>
         </is>
       </c>
     </row>
@@ -2279,142 +3362,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>group_or_company</t>
+          <t>layer</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>source</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>finding</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>key_number</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>spacex_decision_rule</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Small IPOs</t>
+          <t>Broad IPO prior</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Excluded</t>
+          <t>Study 15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Below $5B IPO market cap or below $500M proceeds.</t>
+          <t>Day-1-close IPO chasing is a negative base-rate trade.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>365d median excess vs SPY -28.4%; only 19% beat SPY.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Start from skepticism; do not buy SpaceX just because the IPO is famous.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SPACs/de-SPACs</t>
+          <t>Quality filter</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Excluded</t>
+          <t>Study 24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Different incentives, redemption mechanics and sponsor economics.</t>
+          <t>Small/noisy IPOs are removed; only institutional-scale comps remain.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Filtered 6m comp median from first close -14.7%.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Quality filter reduces junk risk but still leaves post-IPO fade risk.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Biotech binary names</t>
+          <t>Scarcity and index flow</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Excluded</t>
+          <t>Study 24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Clinical-binary risk is not comparable to SpaceX.</t>
+          <t>SpaceX has unusually tight immediate tradable supply plus a Nasdaq-100 fast-entry path.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Immediate float 4.25%; Nasdaq low-float modified market cap about $225B.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Treat early upside as flow/scarcity, not proof of long-term entry quality.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Firefly Aerospace</t>
+          <t>Unlock and governance penalty</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Context only</t>
+          <t>Study 24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Useful space-sector context, not a SpaceX-scale valuation or liquidity comp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Excluded from core</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Passes size floor but retail/social-media profile would overweight meme-demand mechanics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Instacart</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Excluded from core</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Not small by market cap, but lower-quality business comparability and smaller offering.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Context only</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Large direct listing, but no primary proceeds and no lead-underwriter execution.</t>
+          <t>First-six-month releases, Musk control and registration-rights overhang cap public-entry quality.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Q2/Q3 earnings unlocks plus 70/90/105/120/135/180-day releases are multiples of IPO float.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Wait for unlock absorption before underwriting a larger long-term position.</t>
         </is>
       </c>
     </row>
@@ -2429,294 +3511,448 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>underwriter</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>rule_area</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>quality_score</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>spacex_read</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>first_6m_model_impact</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fast Entry</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>IPO can skip the normal three-full-calendar-month seasoning rule if its Full Market Capitalization ranks within the top 40 current Nasdaq-100 constituents. It is evaluated after the 7th trading day and typically added after 15 trading days, with announcement after the 10th trading day.</t>
-        </is>
+          <t>Joint bookrunner / lead-left group</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Likely eligible if SPCX lists on an eligible Nasdaq market and no final filing changes the share count. At $1.77T basic market cap, the top-40 size test should not be the gating item.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Creates a near-term QQQ/NDX flow catalyst around late June to early July 2026, not a day-one inclusion.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Nasdaq-100 Index Methodology</t>
+          <t>Top-tier mega-cap IPO franchise and stabilization credibility.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Liquidity</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Standard liquidity screen is three-month ADVT of at least $5M. For IPO fast entry, ADVT is measured from first trading day through the applicable reference date.</t>
-        </is>
+          <t>Joint bookrunner / lead-left group</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A $75B IPO should almost certainly clear $5M ADVT, but this cannot be final until trading occurs.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Liquidity is a check-the-box risk, not the main risk.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Nasdaq-100 Index Methodology</t>
+          <t>Top-tier technology IPO franchise; stabilization agent per S-1/A.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
+          <t>BofA Securities</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Free float</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>No minimum free-float criterion. For low-float securities, index weighting uses the lesser of reported TSO or 3x free-floating shares.</t>
-        </is>
+          <t>Joint bookrunner</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4.5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Base IPO float is 555.6M shares, or 4.25% of basic shares. Initial NDX modified market cap is about $225.0B, not the full $1765.2B company value.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>The rule allows inclusion but scales the starting weight to tradable supply. This reduces, but does not eliminate, forced-buy pressure.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Nasdaq-100 Index Methodology</t>
+          <t>Top global distribution and lending relationship.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quarterly path</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>The updated framework adds rank-based quarterly reviews in March, June and September, plus the annual December reconstitution.</t>
-        </is>
+          <t>Joint bookrunner</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>If fast entry were missed for an operational reason, the next scheduled framework matters. The first quarterly rebalance under the new rules is June 22, 2026.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Index demand can arrive in tranches rather than only at December reconstitution.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Nasdaq methodology update</t>
+          <t>Top global distribution; strong cross-border reach.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>J.P. Morgan</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Seasoning</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>IPOs should trade on an eligible exchange for at least 12 months before consideration for S&amp;P Composite 1500 inclusion. No IPO fast track is allowed for S&amp;P Composite 1500 candidates.</t>
-        </is>
+          <t>Joint bookrunner</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Assuming first trade on June 12, 2026, the earliest simple seasoning date is June 12, 2027. This is only a possible consideration date, not an inclusion guarantee.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>No S&amp;P 500 forced-buy catalyst in the first six months.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>S&amp;P U.S. Indices Methodology; S&amp;P MegaCap consultation results</t>
+          <t>Top global equity capital markets franchise.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Financial viability</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>GAAP net income from continuing operations must be positive for the most recent quarter and for the sum of the most recent four consecutive quarters.</t>
-        </is>
+          <t>Joint bookrunner</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SpaceX reported a 2025 net loss and a Q1 2026 net loss. It does not currently clear the profitability screen.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Even after 12 months, S&amp;P 500 inclusion likely requires a demonstrated profit turn.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>S&amp;P U.S. Indices Methodology; S&amp;P MegaCap consultation results</t>
+          <t>Strong global technology/industrial ECM distribution.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>Deutsche Bank Securities</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Float and liquidity</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>S&amp;P Composite 1500 additions require IWF of at least 0.10, security-level FMC of at least 50% of the index market-cap threshold, FALR of at least 0.75, and at least 250,000 shares traded in each of the six months before evaluation.</t>
-        </is>
+          <t>Joint bookrunner</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Base IPO float is only 4.25% of basic shares, below the 10% IWF screen if only IPO shares count. Lock-up releases could change this later.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Float unlocks matter for S&amp;P eligibility, but they also create supply risk.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>S&amp;P U.S. Indices Methodology; S&amp;P MegaCap consultation results</t>
+          <t>Global bank; useful international distribution.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S&amp;P Total Market / Dow Jones U.S. Total Stock Market</t>
+          <t>Wells Fargo Securities</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mega-cap broad-index update</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Effective June 8, 2026, broad-market indices allow an alternative IWF path for mega-cap companies and preserve IPO fast-track treatment when all other criteria are met.</t>
-        </is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Base float-adjusted market cap is about $75.0B, so broad-index eligibility may arrive much earlier than S&amp;P 500 eligibility.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Potential total-market ETF flow is relevant, but it should not be confused with S&amp;P 500 membership.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>S&amp;P MegaCap consultation results</t>
+          <t>Large U.S. distribution and lending relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Allen &amp; Company</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Elite tech/media relationship bank; narrower distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cantor</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Distribution support; not lead franchise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Needham</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Growth/technology distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Raymond James</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Retail and middle-market distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Societe Generale</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>European distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stifel</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Retail and growth distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>William Blair</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Growth-company distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BTG Pactual</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Latin America distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ING</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>European distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Macquarie Capital</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Asia-Pacific/infrastructure distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mirae Asset Securities</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Asia distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Mizuho</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Japan/global distribution support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bookrunner</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>European/Latin America distribution support.</t>
         </is>
       </c>
     </row>
@@ -2731,161 +3967,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>segment</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>revenue_2025_usd_b</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>model_date</t>
+          <t>operating_income_2025_usd_b</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>adjusted_ebitda_2025_usd_b</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capex_2025_usd_b</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>revenue_q1_2026_usd_b</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>operating_income_q1_2026_usd_b</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda_q1_2026_usd_b</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>capex_q1_2026_usd_b</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>business_quality_score</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>note</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>operating_margin_2025_pct</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>capex_to_revenue_2025_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>First trade assumption</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SPCX begins trading</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Assumption based on June 2026 launch timing; update once 424B4/final exchange notice is filed.</t>
-        </is>
+          <t>Space</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4.086</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.657</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.832</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.662</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.351</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Launch cadence and vertical integration are elite; still loss-making in Q1 and Starship execution is key.</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>-16.07929515418502</v>
+      </c>
+      <c r="M2" t="n">
+        <v>93.78365149290261</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nasdaq-100 IPO reference date</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>7th trading day evaluation</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Full market cap top-40 test and fast-entry eligibility check.</t>
-        </is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11.387</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4.423</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7.168</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.178</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.257</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.087</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.332</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Best current business: 2025 operating margin 38.8%, subscribers 8.9M at year-end and 10.3M Q1 2026; ARPU declining from $99 in 2023 to $66 Q1 2026.</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>38.84253973829806</v>
+      </c>
+      <c r="M3" t="n">
+        <v>36.69096337929217</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nasdaq-100 announcement window</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>10th trading day announcement</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Methodology says announcement typically occurs after close on the 10th trading day.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Nasdaq-100 addition window</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>15th trading day typical addition</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Methodology says IPO fast-entry addition typically occurs after 15 trading days; effective date can depend on notice conventions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>S&amp;P broad-index fast-track</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>S&amp;P TMI / Dow Jones TSM possible fast-track</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Depends on S&amp;P DJI announcement and all applicable criteria; this is not S&amp;P 500.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>S&amp;P 500 earliest seasoning date</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>12 months after first trade</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2027-06-12</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Only a possible consideration date. Profitability, IWF, liquidity and committee selection still apply.</t>
-        </is>
+          <t>AI/xAI/X</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.201</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-6.355</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.237</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12.727</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-2.469</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.609</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7.723</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Biggest upside and biggest quality penalty: $12.7B 2025 capex, large operating losses, related-party and regulatory complexity; Anthropic/Google contracts improve revenue visibility but are terminable.</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>-198.5317088409872</v>
+      </c>
+      <c r="M4" t="n">
+        <v>397.5945017182131</v>
       </c>
     </row>
   </sheetData>
@@ -2899,123 +4183,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>SpaceX IPO model stance</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>case</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>revenue_usd_b</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>implied_market_cap_usd_b</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>price_to_sales_x</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Trade-only / wait-for-unlock bias at IPO valuation.</t>
+          <t>2025 reported revenue</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>18.674</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1765.241798625</v>
+      </c>
+      <c r="D2" t="n">
+        <v>94.52938838090392</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Contract run-rate cases are not risk-adjusted; Anthropic/Google contracts are terminable and delivery-dependent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Q1 2026 annualized</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>18.776</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1765.241798625</v>
+      </c>
+      <c r="D3" t="n">
+        <v>94.01586059996804</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Contract run-rate cases are not risk-adjusted; Anthropic/Google contracts are terminable and delivery-dependent.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Key numbers</t>
+          <t>2025 revenue + Anthropic annualized run-rate</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>33.674</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1765.241798625</v>
+      </c>
+      <c r="D4" t="n">
+        <v>52.42150616573617</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Contract run-rate cases are not risk-adjusted; Anthropic/Google contracts are terminable and delivery-dependent.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Immediate base free float</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>555.6M shares (4.25% of basic shares)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Implied basic market cap</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>$1765.2B</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Class B voting power</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>88.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Musk combined voting power</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>84.4% after offering per S-1/A table</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>First-six-month issue</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>IPO float scarcity can support the tape, but cumulative tradable supply reaches about 9.4x IPO float by day 180 in both release scenarios.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Nasdaq-100 path</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Fast Entry can evaluate a mega IPO on trading day 7 and typically add after trading day 15; low-float weight is capped at 3x free float.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>S&amp;P 500 path</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>No mega-cap fast track: 12-month IPO seasoning, positive GAAP income screens and IWF/liquidity screens remain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Day-180 lock-up ratio</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Performance case: 5.23B shares / 9.42x IPO float / 40.0% of basic shares. No-performance case: 5.25B shares / 9.44x / 40.1%.</t>
+          <t>2025 revenue + Anthropic + Google annualized run-rate</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>44.714</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1765.241798625</v>
+      </c>
+      <c r="D5" t="n">
+        <v>39.47850334626738</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Contract run-rate cases are not risk-adjusted; Anthropic/Google contracts are terminable and delivery-dependent.</t>
         </is>
       </c>
     </row>
@@ -3665,6 +4943,757 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>group_or_company</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Small IPOs</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Below $5B IPO market cap or below $500M proceeds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SPACs/de-SPACs</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Different incentives, redemption mechanics and sponsor economics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Biotech binary names</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Clinical-binary risk is not comparable to SpaceX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Firefly Aerospace</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Useful space-sector context, not a SpaceX-scale valuation or liquidity comp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Excluded from core</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Passes size floor but retail/social-media profile would overweight meme-demand mechanics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Excluded from core</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Not small by market cap, but lower-quality business comparability and smaller offering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Context only</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Large direct listing, but no primary proceeds and no lead-underwriter execution.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>rule_area</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>spacex_read</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>first_6m_model_impact</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fast Entry</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IPO can skip the normal three-full-calendar-month seasoning rule if its Full Market Capitalization ranks within the top 40 current Nasdaq-100 constituents. It is evaluated after the 7th trading day and typically added after 15 trading days, with announcement after the 10th trading day.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Likely eligible if SPCX lists on an eligible Nasdaq market and no final filing changes the share count. At $1.77T basic market cap, the top-40 size test should not be the gating item.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Creates a near-term QQQ/NDX flow catalyst around late June to early July 2026, not a day-one inclusion.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nasdaq-100 Index Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Liquidity</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Standard liquidity screen is three-month ADVT of at least $5M. For IPO fast entry, ADVT is measured from first trading day through the applicable reference date.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A $75B IPO should almost certainly clear $5M ADVT, but this cannot be final until trading occurs.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Liquidity is a check-the-box risk, not the main risk.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nasdaq-100 Index Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Free float</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>No minimum free-float criterion. For low-float securities, index weighting uses the lesser of reported TSO or 3x free-floating shares.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Base IPO float is 555.6M shares, or 4.25% of basic shares. Initial NDX modified market cap is about $225.0B, not the full $1765.2B company value.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>The rule allows inclusion but scales the starting weight to tradable supply. This reduces, but does not eliminate, forced-buy pressure.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nasdaq-100 Index Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Quarterly path</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>The updated framework adds rank-based quarterly reviews in March, June and September, plus the annual December reconstitution.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>If fast entry were missed for an operational reason, the next scheduled framework matters. The first quarterly rebalance under the new rules is June 22, 2026.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Index demand can arrive in tranches rather than only at December reconstitution.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nasdaq methodology update</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Seasoning</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>IPOs should trade on an eligible exchange for at least 12 months before consideration for S&amp;P Composite 1500 inclusion. No IPO fast track is allowed for S&amp;P Composite 1500 candidates.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Assuming first trade on June 12, 2026, the earliest simple seasoning date is June 12, 2027. This is only a possible consideration date, not an inclusion guarantee.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>No S&amp;P 500 forced-buy catalyst in the first six months.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>S&amp;P U.S. Indices Methodology; S&amp;P MegaCap consultation results</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Financial viability</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GAAP net income from continuing operations must be positive for the most recent quarter and for the sum of the most recent four consecutive quarters.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SpaceX reported a 2025 net loss and a Q1 2026 net loss. It does not currently clear the profitability screen.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Even after 12 months, S&amp;P 500 inclusion likely requires a demonstrated profit turn.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>S&amp;P U.S. Indices Methodology; S&amp;P MegaCap consultation results</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Float and liquidity</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>S&amp;P Composite 1500 additions require IWF of at least 0.10, security-level FMC of at least 50% of the index market-cap threshold, FALR of at least 0.75, and at least 250,000 shares traded in each of the six months before evaluation.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Base IPO float is only 4.25% of basic shares, below the 10% IWF screen if only IPO shares count. Lock-up releases could change this later.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Float unlocks matter for S&amp;P eligibility, but they also create supply risk.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>S&amp;P U.S. Indices Methodology; S&amp;P MegaCap consultation results</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S&amp;P Total Market / Dow Jones U.S. Total Stock Market</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mega-cap broad-index update</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Effective June 8, 2026, broad-market indices allow an alternative IWF path for mega-cap companies and preserve IPO fast-track treatment when all other criteria are met.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Base float-adjusted market cap is about $75.0B, so broad-index eligibility may arrive much earlier than S&amp;P 500 eligibility.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Potential total-market ETF flow is relevant, but it should not be confused with S&amp;P 500 membership.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>S&amp;P MegaCap consultation results</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>model_date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>First trade assumption</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SPCX begins trading</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Assumption based on June 2026 launch timing; update once 424B4/final exchange notice is filed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nasdaq-100 IPO reference date</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7th trading day evaluation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Full market cap top-40 test and fast-entry eligibility check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nasdaq-100 announcement window</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10th trading day announcement</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Methodology says announcement typically occurs after close on the 10th trading day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nasdaq-100 addition window</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>15th trading day typical addition</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Methodology says IPO fast-entry addition typically occurs after 15 trading days; effective date can depend on notice conventions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S&amp;P broad-index fast-track</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S&amp;P TMI / Dow Jones TSM possible fast-track</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Depends on S&amp;P DJI announcement and all applicable criteria; this is not S&amp;P 500.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 earliest seasoning date</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12 months after first trade</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2027-06-12</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Only a possible consideration date. Profitability, IWF, liquidity and committee selection still apply.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SpaceX IPO model stance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Trade-only / wait-for-unlock bias at IPO valuation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Key numbers</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Immediate base free float</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>555.6M shares (4.25% of basic shares)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Implied basic market cap</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>$1765.2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Class B voting power</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>88.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Musk combined voting power</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>84.4% after offering per S-1/A table</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>First-six-month issue</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IPO float scarcity can support the tape, but cumulative tradable supply reaches about 9.4x IPO float by day 180 in both release scenarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Nasdaq-100 path</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fast Entry can evaluate a mega IPO on trading day 7 and typically add after trading day 15; low-float weight is capped at 3x free float.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 path</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>No mega-cap fast track: 12-month IPO seasoning, positive GAAP income screens and IWF/liquidity screens remain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Day-180 lock-up ratio</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Performance case: 5.23B shares / 9.42x IPO float / 40.0% of basic shares. No-performance case: 5.25B shares / 9.44x / 40.1%.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3911,7 +5940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3962,20 +5991,35 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>event_date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>date_basis</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>date_precision</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>release_x_base_ipo_float</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>release_pct_basic_common</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>release_pct_post_class_a</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>release_pct_relevant_pool</t>
         </is>
@@ -4019,16 +6063,31 @@
       <c r="I2" t="b">
         <v>1</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>At offering</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>4.248709722567172</v>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>7.527652199187732</v>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -4068,16 +6127,31 @@
       <c r="I3" t="b">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>30 days after prospectus</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>0.1499999995499999</v>
       </c>
-      <c r="K3" t="n">
+      <c r="N3" t="n">
         <v>0.6373064564731565</v>
       </c>
-      <c r="L3" t="n">
+      <c r="O3" t="n">
         <v>1.129147826490716</v>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4117,16 +6191,31 @@
       <c r="I4" t="b">
         <v>1</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TBD - likely Aug 2026</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2nd full trading day after Q2 2026 earnings release</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>expected_month</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
         <v>1.6407000016407</v>
       </c>
-      <c r="K4" t="n">
+      <c r="N4" t="n">
         <v>6.970858048786818</v>
       </c>
-      <c r="L4" t="n">
+      <c r="O4" t="n">
         <v>12.35061897555793</v>
       </c>
-      <c r="M4" t="n">
+      <c r="P4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -4168,16 +6257,31 @@
       <c r="I5" t="b">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TBD - likely Aug 2026</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Same Q2 2026 release window</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>expected_month</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
         <v>0.82044000082044</v>
       </c>
-      <c r="K5" t="n">
+      <c r="N5" t="n">
         <v>3.485811408268823</v>
       </c>
-      <c r="L5" t="n">
+      <c r="O5" t="n">
         <v>6.17598697647757</v>
       </c>
-      <c r="M5" t="n">
+      <c r="P5" t="n">
         <v>10.00109709270433</v>
       </c>
     </row>
@@ -4219,16 +6323,31 @@
       <c r="I6" t="b">
         <v>1</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>70th day after prospectus</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
         <v>0.5742000005742</v>
       </c>
-      <c r="K6" t="n">
+      <c r="N6" t="n">
         <v>2.43960912513768</v>
       </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
         <v>4.322377897095973</v>
       </c>
-      <c r="M6" t="n">
+      <c r="P6" t="n">
         <v>6.999451453647833</v>
       </c>
     </row>
@@ -4270,16 +6389,31 @@
       <c r="I7" t="b">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>90th day after prospectus</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
         <v>0.5742000005742</v>
       </c>
-      <c r="K7" t="n">
+      <c r="N7" t="n">
         <v>2.43960912513768</v>
       </c>
-      <c r="L7" t="n">
+      <c r="O7" t="n">
         <v>4.322377897095973</v>
       </c>
-      <c r="M7" t="n">
+      <c r="P7" t="n">
         <v>6.999451453647833</v>
       </c>
     </row>
@@ -4321,16 +6455,31 @@
       <c r="I8" t="b">
         <v>1</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>91st day after prospectus</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
         <v>0.10638000010638</v>
       </c>
-      <c r="K8" t="n">
+      <c r="N8" t="n">
         <v>0.4519777407386735</v>
       </c>
-      <c r="L8" t="n">
+      <c r="O8" t="n">
         <v>0.8007916417503825</v>
       </c>
-      <c r="M8" t="n">
+      <c r="P8" t="n">
         <v>1.296763576522216</v>
       </c>
     </row>
@@ -4372,16 +6521,31 @@
       <c r="I9" t="b">
         <v>1</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>105th day after prospectus</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
         <v>0.5911200005911199</v>
       </c>
-      <c r="K9" t="n">
+      <c r="N9" t="n">
         <v>2.511497293715404</v>
       </c>
-      <c r="L9" t="n">
+      <c r="O9" t="n">
         <v>4.449745772433598</v>
       </c>
-      <c r="M9" t="n">
+      <c r="P9" t="n">
         <v>7.205704882062534</v>
       </c>
     </row>
@@ -4423,16 +6587,31 @@
       <c r="I10" t="b">
         <v>1</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>120th day after prospectus</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
         <v>0.5911200005911199</v>
       </c>
-      <c r="K10" t="n">
+      <c r="N10" t="n">
         <v>2.511497293715404</v>
       </c>
-      <c r="L10" t="n">
+      <c r="O10" t="n">
         <v>4.449745772433598</v>
       </c>
-      <c r="M10" t="n">
+      <c r="P10" t="n">
         <v>7.205704882062534</v>
       </c>
     </row>
@@ -4474,16 +6653,31 @@
       <c r="I11" t="b">
         <v>1</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>135th day after prospectus</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
         <v>0.5911200005911199</v>
       </c>
-      <c r="K11" t="n">
+      <c r="N11" t="n">
         <v>2.511497293715404</v>
       </c>
-      <c r="L11" t="n">
+      <c r="O11" t="n">
         <v>4.449745772433598</v>
       </c>
-      <c r="M11" t="n">
+      <c r="P11" t="n">
         <v>7.205704882062534</v>
       </c>
     </row>
@@ -4525,16 +6719,31 @@
       <c r="I12" t="b">
         <v>1</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TBD - likely Nov 2026</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2nd full trading day after Q3 2026 earnings release</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>expected_month</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
         <v>2.34000000234</v>
       </c>
-      <c r="K12" t="n">
+      <c r="N12" t="n">
         <v>9.941980760749166</v>
       </c>
-      <c r="L12" t="n">
+      <c r="O12" t="n">
         <v>17.614706163714</v>
       </c>
-      <c r="M12" t="n">
+      <c r="P12" t="n">
         <v>28.52441031267142</v>
       </c>
     </row>
@@ -4576,16 +6785,31 @@
       <c r="I13" t="b">
         <v>1</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>180th day after prospectus</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
         <v>0.5911200005911199</v>
       </c>
-      <c r="K13" t="n">
+      <c r="N13" t="n">
         <v>2.511497293715404</v>
       </c>
-      <c r="L13" t="n">
+      <c r="O13" t="n">
         <v>4.449745772433598</v>
       </c>
-      <c r="M13" t="n">
+      <c r="P13" t="n">
         <v>7.205704882062534</v>
       </c>
     </row>
@@ -4627,16 +6851,31 @@
       <c r="I14" t="b">
         <v>1</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>180th day after prospectus</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
         <v>1.43568000143568</v>
       </c>
-      <c r="K14" t="n">
+      <c r="N14" t="n">
         <v>6.099787580595026</v>
       </c>
-      <c r="L14" t="n">
+      <c r="O14" t="n">
         <v>10.80729972013714</v>
       </c>
-      <c r="M14" t="n">
+      <c r="P14" t="n">
         <v>17.50082281952825</v>
       </c>
     </row>
@@ -4678,16 +6917,31 @@
       <c r="I15" t="b">
         <v>0</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TBD - likely Mar 2027</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2nd full trading day after Q4 2026 earnings release</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>expected_month</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
         <v>0.63342000063342</v>
       </c>
-      <c r="K15" t="n">
+      <c r="N15" t="n">
         <v>2.691217715159716</v>
       </c>
-      <c r="L15" t="n">
+      <c r="O15" t="n">
         <v>4.768165460777658</v>
       </c>
-      <c r="M15" t="n">
+      <c r="P15" t="n">
         <v>5.4984375</v>
       </c>
     </row>
@@ -4729,16 +6983,31 @@
       <c r="I16" t="b">
         <v>0</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2027-03-18</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>280th day after prospectus</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
         <v>0.3168000003168</v>
       </c>
-      <c r="K16" t="n">
+      <c r="N16" t="n">
         <v>1.345991241455271</v>
       </c>
-      <c r="L16" t="n">
+      <c r="O16" t="n">
         <v>2.384760219087434</v>
       </c>
-      <c r="M16" t="n">
+      <c r="P16" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -4780,16 +7049,31 @@
       <c r="I17" t="b">
         <v>0</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>TBD - likely May 2027</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2nd full trading day after Q1 2027 earnings release</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>expected_month</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
         <v>0.63342000063342</v>
       </c>
-      <c r="K17" t="n">
+      <c r="N17" t="n">
         <v>2.691217715159716</v>
       </c>
-      <c r="L17" t="n">
+      <c r="O17" t="n">
         <v>4.768165460777658</v>
       </c>
-      <c r="M17" t="n">
+      <c r="P17" t="n">
         <v>5.4984375</v>
       </c>
     </row>
@@ -4831,16 +7115,31 @@
       <c r="I18" t="b">
         <v>0</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2027-05-17</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>340th day after prospectus</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
         <v>0.3168000003168</v>
       </c>
-      <c r="K18" t="n">
+      <c r="N18" t="n">
         <v>1.345991241455271</v>
       </c>
-      <c r="L18" t="n">
+      <c r="O18" t="n">
         <v>2.384760219087434</v>
       </c>
-      <c r="M18" t="n">
+      <c r="P18" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -4882,16 +7181,31 @@
       <c r="I19" t="b">
         <v>0</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2027-06-12</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>366th day after prospectus</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
         <v>0.63342000063342</v>
       </c>
-      <c r="K19" t="n">
+      <c r="N19" t="n">
         <v>2.691217715159716</v>
       </c>
-      <c r="L19" t="n">
+      <c r="O19" t="n">
         <v>4.768165460777658</v>
       </c>
-      <c r="M19" t="n">
+      <c r="P19" t="n">
         <v>5.4984375</v>
       </c>
     </row>
@@ -4933,16 +7247,31 @@
       <c r="I20" t="b">
         <v>0</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2027-06-12</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>366th day after prospectus</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
         <v>11.52000001152</v>
       </c>
-      <c r="K20" t="n">
+      <c r="N20" t="n">
         <v>48.94513605291896</v>
       </c>
-      <c r="L20" t="n">
+      <c r="O20" t="n">
         <v>86.71855342136122</v>
       </c>
-      <c r="M20" t="n">
+      <c r="P20" t="n">
         <v>100</v>
       </c>
     </row>
@@ -4984,16 +7313,31 @@
       <c r="I21" t="b">
         <v>0</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>TBD - likely Aug 2027</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2nd full trading day after Q2 2027 earnings release</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>expected_month</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
         <v>0.63342000063342</v>
       </c>
-      <c r="K21" t="n">
+      <c r="N21" t="n">
         <v>2.691217715159716</v>
       </c>
-      <c r="L21" t="n">
+      <c r="O21" t="n">
         <v>4.768165460777658</v>
       </c>
-      <c r="M21" t="n">
+      <c r="P21" t="n">
         <v>5.4984375</v>
       </c>
     </row>
@@ -5222,7 +7566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5311,6 +7655,21 @@
           <t>note</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>event_date</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>date_basis</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>date_precision</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -5372,6 +7731,21 @@
           <t>Starting tradable Class A supply.</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>At offering</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -5433,6 +7807,21 @@
           <t>20% release from 180-day pool.</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>TBD - likely Aug 2026</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Q2 2026 earnings window</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>expected_month</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5494,6 +7883,21 @@
           <t>Only in performance case: price at least 30% above IPO price for 5 of 10 trading days.</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>TBD - likely Aug 2026</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Q2 2026 earnings window</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>expected_month</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -5555,6 +7959,21 @@
           <t>7% release from 180-day pool.</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>70th day after prospectus</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -5616,6 +8035,21 @@
           <t>7% release from 180-day pool.</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>90th day after prospectus</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -5677,6 +8111,21 @@
           <t>Rule 144 timing catch-up; shown as incremental tradable supply, not a new percentage tranche.</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>91st day after prospectus</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5738,6 +8187,21 @@
           <t>7% release from 180-day pool.</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>105th day after prospectus</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5799,6 +8263,21 @@
           <t>7% release from 180-day pool.</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>120th day after prospectus</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5860,6 +8339,21 @@
           <t>7% release from 180-day pool.</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>135th day after prospectus</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5921,6 +8415,21 @@
           <t>28% release from 180-day pool.</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>TBD - likely Nov 2026</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Q3 2026 earnings window</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>expected_month</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5980,6 +8489,21 @@
       <c r="Q12" t="inlineStr">
         <is>
           <t>Final 180-day release is smaller if the performance release happened, larger if it did not.</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>180th day after prospectus</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>model_calendar_date</t>
         </is>
       </c>
     </row>
@@ -5994,579 +8518,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ticker</t>
+          <t>concept</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>plain_english</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>inclusion_tier</t>
+          <t>company_meaning</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>management_quality</t>
+          <t>investor_meaning</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>business_quality</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ipo_quality</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>governance_quality</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>market_setup</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>weighted_quality_score</t>
+          <t>equity_supply_answer</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SPCX</t>
+          <t>Nasdaq exchange listing</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>A company trades on the Nasdaq exchange. This is a listing venue, like NYSE versus Nasdaq.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Subject</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Elite execution and underwriting; penalized for control, related parties, AI losses and unlock overhang.</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>3.625</v>
+          <t>Lets the shares trade publicly under the ticker, subject to exchange listing standards.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Gives investors a public trading venue and continuous price discovery.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>No. Listing does not create extra equity beyond the shares sold or registered.</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Nasdaq-100 index inclusion</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>The company becomes a constituent of the Nasdaq-100 index, which is tracked by ETFs and benchmarked products.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Core quality comp</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Best-in-class scaled network IPO; cleaner governance and profitability than SpaceX.</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>4.65</v>
+          <t>Raises visibility, may improve liquidity, and can create passive/index demand. It does not raise new cash for SpaceX.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Can create forced buying and higher liquidity, but it is not a fundamental guarantee and can be offset by valuation or unlock supply.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>No new shares are created. The index assigns a weight to existing shares; for low-float names Nasdaq-100 caps modified market cap at 3x free float.</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>Low-float weighting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Nasdaq-100 has no minimum free-float requirement, but low-float securities are weighted using the lesser of listed shares or 3x free-floating shares.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Core quality comp</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Founder-led cybersecurity compounder with credible underwriting and strong public-market quality.</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>4.225000000000001</v>
+          <t>As more shares unlock and become free floating, the stock could represent more index market cap at later reviews.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Unlocks can increase future index weight but also add sellable supply. The same event can be both passive-demand positive and supply-risk negative.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Base IPO float supports about $225.0B of Nasdaq modified market cap versus $1765.2B full basic market cap.</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>Capital raised</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Index inclusion is secondary-market index mechanics, not a primary offering.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Core quality comp</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>High-quality founder-led software IPO with good governance and durable growth.</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>4.225000000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ABNB</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Airbnb</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Core quality comp</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Founder-led platform with brand quality and strong IPO execution; dual-class governance but less extreme than SpaceX.</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Meta/Facebook</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Scale/control comp</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Best scale and founder-control comp; weak early trading shows scarcity does not immunize valuation.</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>4.225</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ARM</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Arm</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Scale/control comp</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>High-quality tech asset with parent-control overhang; useful float-scarcity comp.</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Uber</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Scale comp</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Large institutional IPO; useful caution on valuation and post-listing profitability questions.</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>3.725</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SNOW</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Valuation caution comp</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Great company, extreme valuation at IPO; useful for pop/fade and valuation discipline.</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>3.825</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DASH</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>DoorDash</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Valuation caution comp</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Founder-led but cyclically expensive IPO; useful first-6-month caution.</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>3.625</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RIVN</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Capital intensity caution comp</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Institutional-scale but capex-heavy story IPO; useful negative comp for AI/Starship capex risk.</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>2.875</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BABA</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Alibaba</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Liquidity-only comp</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Mega IPO liquidity comp; not a clean U.S. governance comp due ADR/China/VIE issues.</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>3.525</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Excluded from core</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Large liquid listing, but direct listing with no primary IPO proceeds or lead underwriter.</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>2.825</v>
+          <t>SpaceX raises capital from the IPO proceeds, not from Nasdaq-100 inclusion itself.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Index funds buy shares from the market or other holders; they do not inject cash into the company unless a separate primary issuance occurs.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>No. Equity outstanding changes only through issuance, conversion, exercise, buyback, or similar corporate actions.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6580,873 +8667,206 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ticker</t>
+          <t>business_line</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ipo_date</t>
+          <t>revenue_2025_usd_b</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ipo_proceeds_usd_b</t>
+          <t>operating_income_2025_usd_b</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ipo_market_cap_usd_b</t>
+          <t>capex_2025_usd_b</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>listing_type</t>
+          <t>revenue_q1_2026_usd_b</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>lead_underwriters</t>
+          <t>operating_income_q1_2026_usd_b</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>inclusion</t>
+          <t>capex_q1_2026_usd_b</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>rationale</t>
+          <t>why_it_matters</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>approx_ipo_public_float_pct</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>float_note</t>
+          <t>key_risks</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SPCX</t>
+          <t>Rocket / Space</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SpaceX</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-06-12 expected trading</t>
-        </is>
+          <t>Falcon, Dragon, Starship and customer launch operations.</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4.086</v>
       </c>
       <c r="D2" t="n">
-        <v>75</v>
+        <v>-0.657</v>
       </c>
       <c r="E2" t="n">
-        <v>1765.7</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Goldman Sachs, Morgan Stanley; large global syndicate</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Subject</t>
-        </is>
+        <v>3.832</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.662</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.052</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Passes scale and underwriting; unique control and AI roll-up risk.</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>4.248709722567172</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Calculated from S-1/A base IPO shares / post-offering basic shares.</t>
+          <t>Strategic moat and launch cadence are the core franchise. Starship is the upside and execution-risk center.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Execution risk, mission failure, capital intensity, government/customer concentration, launch cadence and regulatory approvals.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Starlink / Connectivity</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2008-03-19</t>
-        </is>
+          <t>Starlink broadband/connectivity services and associated offerings.</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>11.387</v>
       </c>
       <c r="D3" t="n">
-        <v>17.9</v>
+        <v>4.423</v>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>J.P. Morgan, Goldman Sachs, BofA</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
+        <v>4.178</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.257</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.332</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Large, profitable, high-quality operating company.</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>42.61904761904762</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+          <t>Best current business quality: 2025 operating margin 38.8%, 8.9M subscribers at year-end 2025 and 10.3M in Q1 2026.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ARPU declined from $99 in 2023 to $81 in 2025 and $66 in Q1 2026; spectrum, orbital, regulatory and capacity constraints matter.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AI / xAI / X</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Meta/Facebook</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2012-05-18</t>
-        </is>
+          <t>AI compute, Grok, X platform and related AI infrastructure acquired through xAI/X transactions.</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3.201</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>-6.355</v>
       </c>
       <c r="E4" t="n">
-        <v>104</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Morgan Stanley, J.P. Morgan, Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
+        <v>12.727</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-2.469</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7.723</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Founder-control and mega-liquidity comp.</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>15.38461538461538</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+          <t>Largest optionality and largest quality penalty. SpaceX acquired xAI effective 2026-02-02; xAI had acquired X Holdings effective 2025-03-28.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Heavy losses, high capex, power/GPU execution, related-party complexity, platform moderation/regulatory risk and terminable compute contracts.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>Cursor / Anysphere</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alibaba</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E5" t="n">
-        <v>168</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Primary IPO / ADR</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Credit Suisse, Deutsche Bank, Goldman Sachs, J.P. Morgan, Morgan Stanley, Citi</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Scale only</t>
-        </is>
-      </c>
+          <t>April 2026 compute plus option agreement with Anysphere, Inc., doing business as Cursor.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Largest historical IPO comp; governance/geography not clean.</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>12.97619047619048</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Uber</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2019-05-10</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Morgan Stanley, Goldman Sachs, BofA</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Large growth IPO with profitability debate.</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>10.72847682119205</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ABNB</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Airbnb</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2020-12-10</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>47</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Morgan Stanley, Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Founder-led platform quality comp.</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>7.446808510638298</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ARM</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Arm</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2023-09-14</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E8" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Barclays, Goldman Sachs, J.P. Morgan, Mizuho</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>High-quality controlled-company float-scarcity comp.</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>8.990825688073395</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SNOW</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>33</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Goldman Sachs, Morgan Stanley, J.P. Morgan</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Quality company, valuation-risk comp.</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>10.3030303030303</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DASH</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>DoorDash</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2020-12-09</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E10" t="n">
-        <v>39</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Goldman Sachs, J.P. Morgan</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Founder-led but valuation-sensitive growth IPO.</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>8.717948717948717</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RIVN</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="E11" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Morgan Stanley, Goldman Sachs, J.P. Morgan</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Capital-intensity and story-stock caution comp.</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>17.89473684210526</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CRWD</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Goldman Sachs, J.P. Morgan, BofA, Barclays</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Passes lower bound; high-quality software/security comp.</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>8.823529411764707</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DDOG</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Datadog</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2019-09-19</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Morgan Stanley, Goldman Sachs, J.P. Morgan</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Passes lower bound; high-quality software/infrastructure comp.</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>7.692307692307693</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2021-04-14</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Direct listing</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Excluded from core</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Useful retail/liquidity context, but no primary IPO proceeds or underwriting comp.</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>RDDT</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2024-03-21</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Morgan Stanley, Goldman Sachs, J.P. Morgan</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Passes market-cap floor but too retail/social-media specific for SpaceX core comp.</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>11.71875</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CAVA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Cava</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>J.P. Morgan, Jefferies, Citi</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Below $5B IPO market-cap filter.</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CART</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Instacart/Maplebear</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2023-09-19</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E17" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Primary IPO</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Goldman Sachs, J.P. Morgan</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Weaker business-quality comparability and smaller offering.</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>6.666666666666667</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Approximate: IPO proceeds / IPO market cap, excluding over-allotment and secondary-seller details.</t>
+          <t>Not acquired as of the S-1/A. SpaceX has the right, not obligation, to acquire Cursor at a $60B implied equity value after the offering.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Potential strategic AI coding distribution and training-data asset; also creates option/termination-fee complexity.</t>
         </is>
       </c>
     </row>
@@ -7461,400 +8881,222 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ticker</t>
+          <t>event_date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>first_trade_date</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>first_close_adj_usd</t>
+          <t>date_precision</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>return_from_first_close_1d_pct</t>
+          <t>note</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>return_from_first_close_1m_pct</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>return_from_first_close_3m_pct</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>return_from_first_close_6m_pct</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
+          <t>date_basis</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2012-05-18</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>37.93</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-11</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-50.2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-40</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
+          <t>Twitter acquisition by X Holdings</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>actual_month</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>X Holdings acquired Twitter in October 2022, before the later xAI and SpaceX common-control transactions.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SpaceX S-1/A and FWPs</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>89.17</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-6</v>
-      </c>
-      <c r="F3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
+          <t>Twitter rebranded to X</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>actual_month</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>S-1/A describes impairment of the Twitter brand when Twitter was rebranded to X in July 2023.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SpaceX S-1/A and FWPs</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2008-03-19</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>12.42</v>
-      </c>
-      <c r="D4" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E4" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
+          <t>xAI acquired X Holdings/X</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>actual_effective_date</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>S-1/A says X Holdings was acquired by xAI effective March 28, 2025.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SpaceX S-1/A and FWPs</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2019-05-10</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>41.57</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-10.8</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-34.1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
+          <t>SpaceX acquired xAI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>actual_effective_date</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>S-1/A says X.AI Holdings Corp. was acquired by SpaceX effective February 2, 2026.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SpaceX S-1/A and FWPs</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2020-12-10</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>144.71</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="E6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
+          <t>SpaceX entered Cursor compute + option agreement</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>actual_month</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SpaceX entered a compute and option agreement with Anysphere/Cursor in April 2026.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SpaceX S-1/A and FWPs</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>63.59</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-20.1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
+          <t>Anthropic cloud services agreements</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>actual_month</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SpaceX entered Anthropic cloud services agreements in May 2026 for approximately 325,000 NVIDIA GPUs.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SpaceX S-1/A and FWPs</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>253.93</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-14.7</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DASH</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2020-12-09</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>189.51</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-25.1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-18.7</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RIVN</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>100.73</v>
-      </c>
-      <c r="D10" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-35.7</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-75.90000000000001</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CRWD</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>58</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E11" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="F11" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-18</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>DDOG</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2019-09-19</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>37.55</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-15.9</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-11.1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>yfinance adjusted close downloaded 2026-06-08; returns start at first listed close, not IPO allocation price</t>
+          <t>Google cloud services agreement FWP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>actual_filing_date</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>June 5 FWP disclosed Google agreement for approximately 110,000 NVIDIA GPUs.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SpaceX S-1/A and FWPs</t>
         </is>
       </c>
     </row>

--- a/24-spacex-ipo-quality-model/spacex_ipo_quality_model.xlsx
+++ b/24-spacex-ipo-quality-model/spacex_ipo_quality_model.xlsx
@@ -5940,7 +5940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6006,20 +6006,30 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>milestone_date</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>milestone_with_date</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>release_x_base_ipo_float</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>release_pct_basic_common</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>release_pct_post_class_a</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>release_pct_relevant_pool</t>
         </is>
@@ -6078,16 +6088,26 @@
           <t>model_calendar_date</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>IPO float (2026-06-11)</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>4.248709722567172</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>7.527652199187732</v>
       </c>
-      <c r="P2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -6142,16 +6162,26 @@
           <t>model_calendar_date</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Over-allotment option (2026-07-11)</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>0.1499999995499999</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.6373064564731565</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>1.129147826490716</v>
       </c>
-      <c r="P3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6206,16 +6236,26 @@
           <t>expected_month</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>TBD - likely Aug 2026</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>First earnings release unlock (TBD - likely Aug 2026)</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>1.6407000016407</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>6.970858048786818</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>12.35061897555793</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -6272,16 +6312,26 @@
           <t>expected_month</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>TBD - likely Aug 2026</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Performance early release (TBD - likely Aug 2026)</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>0.82044000082044</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>3.485811408268823</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>6.17598697647757</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>10.00109709270433</v>
       </c>
     </row>
@@ -6338,16 +6388,26 @@
           <t>model_calendar_date</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Day 70 release (2026-08-20)</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>0.5742000005742</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>2.43960912513768</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>4.322377897095973</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>6.999451453647833</v>
       </c>
     </row>
@@ -6404,16 +6464,26 @@
           <t>model_calendar_date</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Day 90 release (2026-09-09)</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>0.5742000005742</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>2.43960912513768</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>4.322377897095973</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>6.999451453647833</v>
       </c>
     </row>
@@ -6470,16 +6540,26 @@
           <t>model_calendar_date</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Affiliate catch-up release (2026-09-10)</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
         <v>0.10638000010638</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.4519777407386735</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.8007916417503825</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>1.296763576522216</v>
       </c>
     </row>
@@ -6536,16 +6616,26 @@
           <t>model_calendar_date</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Day 105 release (2026-09-24)</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
         <v>0.5911200005911199</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>2.511497293715404</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>4.449745772433598</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>7.205704882062534</v>
       </c>
     </row>
@@ -6602,16 +6692,26 @@
           <t>model_calendar_date</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Day 120 release (2026-10-09)</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
         <v>0.5911200005911199</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>2.511497293715404</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>4.449745772433598</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>7.205704882062534</v>
       </c>
     </row>
@@ -6668,16 +6768,26 @@
           <t>model_calendar_date</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Day 135 release (2026-10-24)</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
         <v>0.5911200005911199</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>2.511497293715404</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>4.449745772433598</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>7.205704882062534</v>
       </c>
     </row>
@@ -6734,16 +6844,26 @@
           <t>expected_month</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>TBD - likely Nov 2026</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Q3 2026 earnings release unlock (TBD - likely Nov 2026)</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
         <v>2.34000000234</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>9.941980760749166</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>17.614706163714</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>28.52441031267142</v>
       </c>
     </row>
@@ -6800,16 +6920,26 @@
           <t>model_calendar_date</t>
         </is>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Day 180 final 180-day release (2026-12-08)</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
         <v>0.5911200005911199</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>2.511497293715404</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>4.449745772433598</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>7.205704882062534</v>
       </c>
     </row>
@@ -6866,16 +6996,26 @@
           <t>model_calendar_date</t>
         </is>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Day 180 final 180-day release - no performance release case (2026-12-08)</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
         <v>1.43568000143568</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>6.099787580595026</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>10.80729972013714</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>17.50082281952825</v>
       </c>
     </row>
@@ -6932,16 +7072,26 @@
           <t>expected_month</t>
         </is>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>TBD - likely Mar 2027</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Q4 2026 extended-lock release (TBD - likely Mar 2027)</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
         <v>0.63342000063342</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>2.691217715159716</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>4.768165460777658</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>5.4984375</v>
       </c>
     </row>
@@ -6998,16 +7148,26 @@
           <t>model_calendar_date</t>
         </is>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2027-03-18</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Day 280 extended release (2027-03-18)</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
         <v>0.3168000003168</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>1.345991241455271</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>2.384760219087434</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -7064,16 +7224,26 @@
           <t>expected_month</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>TBD - likely May 2027</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Q1 2027 extended-lock release (TBD - likely May 2027)</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
         <v>0.63342000063342</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>2.691217715159716</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>4.768165460777658</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>5.4984375</v>
       </c>
     </row>
@@ -7130,16 +7300,26 @@
           <t>model_calendar_date</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2027-05-17</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Day 340 extended release (2027-05-17)</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
         <v>0.3168000003168</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>1.345991241455271</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>2.384760219087434</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -7196,16 +7376,26 @@
           <t>model_calendar_date</t>
         </is>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2027-06-12</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Day 366 extended release (2027-06-12)</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
         <v>0.63342000063342</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>2.691217715159716</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>4.768165460777658</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>5.4984375</v>
       </c>
     </row>
@@ -7262,16 +7452,26 @@
           <t>model_calendar_date</t>
         </is>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2027-06-12</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Musk lock-up release (2027-06-12)</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
         <v>11.52000001152</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>48.94513605291896</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>86.71855342136122</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>100</v>
       </c>
     </row>
@@ -7328,16 +7528,26 @@
           <t>expected_month</t>
         </is>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>TBD - likely Aug 2027</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Q2 2027 remaining extended release (TBD - likely Aug 2027)</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
         <v>0.63342000063342</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>2.691217715159716</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>4.768165460777658</v>
       </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
         <v>5.4984375</v>
       </c>
     </row>
@@ -7566,7 +7776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7670,6 +7880,21 @@
           <t>date_precision</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>milestone_date</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>milestone_with_date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -7746,6 +7971,21 @@
           <t>model_calendar_date</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>IPO float</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>IPO float (2026-06-11)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -7822,6 +8062,21 @@
           <t>expected_month</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>TBD - likely Aug 2026</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>First earnings release unlock</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>First earnings release unlock (TBD - likely Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7898,6 +8153,21 @@
           <t>expected_month</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>TBD - likely Aug 2026</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Performance early release</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Performance early release (TBD - likely Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -7974,6 +8244,21 @@
           <t>model_calendar_date</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Day 70 release</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Day 70 release (2026-08-20)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -8050,6 +8335,21 @@
           <t>model_calendar_date</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Day 90 release</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Day 90 release (2026-09-09)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -8126,6 +8426,21 @@
           <t>model_calendar_date</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Affiliate catch-up release</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Affiliate catch-up release (2026-09-10)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -8202,6 +8517,21 @@
           <t>model_calendar_date</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Day 105 release</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Day 105 release (2026-09-24)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8278,6 +8608,21 @@
           <t>model_calendar_date</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Day 120 release</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Day 120 release (2026-10-09)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8354,6 +8699,21 @@
           <t>model_calendar_date</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Day 135 release</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Day 135 release (2026-10-24)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8430,6 +8790,21 @@
           <t>expected_month</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>TBD - likely Nov 2026</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Q3 2026 earnings release unlock</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Q3 2026 earnings release unlock (TBD - likely Nov 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8504,6 +8879,21 @@
       <c r="T12" t="inlineStr">
         <is>
           <t>model_calendar_date</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Day 180 final release</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Day 180 final release (2026-12-08)</t>
         </is>
       </c>
     </row>
